--- a/notebooks/databases/MFRSR_History.xlsx
+++ b/notebooks/databases/MFRSR_History.xlsx
@@ -3,35 +3,36 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Overview" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="451" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="453" sheetId="3" r:id="rId5"/>
-    <sheet state="visible" name="607" sheetId="4" r:id="rId6"/>
-    <sheet state="visible" name="559" sheetId="5" r:id="rId7"/>
-    <sheet state="visible" name="584" sheetId="6" r:id="rId8"/>
-    <sheet state="visible" name="633" sheetId="7" r:id="rId9"/>
-    <sheet state="visible" name="632" sheetId="8" r:id="rId10"/>
-    <sheet state="visible" name="634" sheetId="9" r:id="rId11"/>
-    <sheet state="visible" name="635" sheetId="10" r:id="rId12"/>
-    <sheet state="visible" name="648" sheetId="11" r:id="rId13"/>
-    <sheet state="visible" name="649" sheetId="12" r:id="rId14"/>
-    <sheet state="visible" name="650" sheetId="13" r:id="rId15"/>
-    <sheet state="visible" name="651" sheetId="14" r:id="rId16"/>
-    <sheet state="visible" name="659" sheetId="15" r:id="rId17"/>
-    <sheet state="visible" name="660" sheetId="16" r:id="rId18"/>
-    <sheet state="visible" name="661" sheetId="17" r:id="rId19"/>
-    <sheet state="visible" name="662" sheetId="18" r:id="rId20"/>
-    <sheet state="visible" name="663" sheetId="19" r:id="rId21"/>
-    <sheet state="visible" name="664" sheetId="20" r:id="rId22"/>
-    <sheet state="visible" name="665" sheetId="21" r:id="rId23"/>
-    <sheet state="visible" name="669" sheetId="22" r:id="rId24"/>
-    <sheet state="visible" name="670" sheetId="23" r:id="rId25"/>
-    <sheet state="visible" name="671" sheetId="24" r:id="rId26"/>
-    <sheet state="visible" name="672" sheetId="25" r:id="rId27"/>
-    <sheet state="visible" name="673" sheetId="26" r:id="rId28"/>
-    <sheet state="visible" name="688" sheetId="27" r:id="rId29"/>
-    <sheet state="visible" name="689" sheetId="28" r:id="rId30"/>
-    <sheet state="visible" name="Notes" sheetId="29" r:id="rId31"/>
+    <sheet state="visible" name="Overview" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="451" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="453" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="607" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="559" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="584" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="633" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="632" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="634" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="635" sheetId="10" r:id="rId13"/>
+    <sheet state="visible" name="648" sheetId="11" r:id="rId14"/>
+    <sheet state="visible" name="Sheet8" sheetId="12" r:id="rId15"/>
+    <sheet state="visible" name="649" sheetId="13" r:id="rId16"/>
+    <sheet state="visible" name="650" sheetId="14" r:id="rId17"/>
+    <sheet state="visible" name="651" sheetId="15" r:id="rId18"/>
+    <sheet state="visible" name="659" sheetId="16" r:id="rId19"/>
+    <sheet state="visible" name="660" sheetId="17" r:id="rId20"/>
+    <sheet state="visible" name="661" sheetId="18" r:id="rId21"/>
+    <sheet state="visible" name="662" sheetId="19" r:id="rId22"/>
+    <sheet state="visible" name="663" sheetId="20" r:id="rId23"/>
+    <sheet state="visible" name="664" sheetId="21" r:id="rId24"/>
+    <sheet state="visible" name="665" sheetId="22" r:id="rId25"/>
+    <sheet state="visible" name="669" sheetId="23" r:id="rId26"/>
+    <sheet state="visible" name="670" sheetId="24" r:id="rId27"/>
+    <sheet state="visible" name="671" sheetId="25" r:id="rId28"/>
+    <sheet state="visible" name="672" sheetId="26" r:id="rId29"/>
+    <sheet state="visible" name="673" sheetId="27" r:id="rId30"/>
+    <sheet state="visible" name="688" sheetId="28" r:id="rId31"/>
+    <sheet state="visible" name="689" sheetId="29" r:id="rId32"/>
+    <sheet state="visible" name="Notes" sheetId="30" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -41,16 +42,19 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author/>
+    <author>tc={5af9e62f-a87f-4f00-a2fd-3bc89eae7088}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="F4">
+    <comment authorId="0" xr:uid="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}" ref="F4">
       <text>
-        <t xml:space="preserve">@Gary.Hodges@noaa.gov You mentioned below that this should be $AD23. is that correct? Why not just change it?
-_Assigned to Gary Hodges - NOAA Affiliate_
-	-Hagen Telg - NOAA Affiliate
-I just changed it.  Not sure why I didn't at the time???
-	-Gary Hodges - NOAA Affiliate</t>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@gary.hodges@noaa.gov You mentioned below that this should be $AD23. is that correct? Why not just change it?
+Assigned to gary.hodges@noaa.gov
+Reply:
+	I just changed it.  Not sure why I didn't at the time???
+</t>
       </text>
     </comment>
   </commentList>
@@ -60,14 +64,17 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author/>
+    <author>tc={afa8b239-4954-4803-8f0e-7fe2dbc39426}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B11">
+    <comment authorId="0" xr:uid="{afa8b239-4954-4803-8f0e-7fe2dbc39426}" ref="N35">
       <text>
-        <t xml:space="preserve">@Gary.Hodges@noaa.gov should this read "present"?
-_Assigned to Gary Hodges - NOAA Affiliate_
-	-Hagen Telg - NOAA Affiliate</t>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@gary.hodges@noaa.gov Is this correct?
+Assigned to gary.hodges@noaa.gov
+</t>
       </text>
     </comment>
   </commentList>
@@ -77,14 +84,17 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author/>
+    <author>tc={474bdb03-b157-42c7-bd2d-54363d7a8a2a}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B9">
+    <comment authorId="0" xr:uid="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}" ref="B11">
       <text>
-        <t xml:space="preserve">@Gary.Hodges@noaa.gov should this read "present"?
-_Assigned to Gary Hodges - NOAA Affiliate_
-	-Hagen Telg - NOAA Affiliate</t>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@gary.hodges@noaa.gov should this read "present"?
+Assigned to gary.hodges@noaa.gov
+</t>
       </text>
     </comment>
   </commentList>
@@ -94,19 +104,17 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author/>
+    <author>tc={a6eca3d6-12b0-4885-8774-5cee5686972a}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="C16">
+    <comment authorId="0" xr:uid="{a6eca3d6-12b0-4885-8774-5cee5686972a}" ref="B9">
       <text>
-        <t xml:space="preserve">is this right? I found this empty
-	-Hagen Telg - NOAA Affiliate</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B16">
-      <text>
-        <t xml:space="preserve">is this right?
-	-Hagen Telg - NOAA Affiliate</t>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@gary.hodges@noaa.gov should this read "present"?
+Assigned to gary.hodges@noaa.gov
+</t>
       </text>
     </comment>
   </commentList>
@@ -116,13 +124,28 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author/>
+    <author>tc={3e984a89-391f-4ad1-aa44-03eb9af178d6}</author>
+    <author>tc={949a4adf-7cc6-4586-b634-bfc5a0fb4cf7}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="A6">
+    <comment authorId="0" xr:uid="{3e984a89-391f-4ad1-aa44-03eb9af178d6}" ref="B16">
       <text>
-        <t xml:space="preserve">This is not the exact date! I just put this in in order to have a valid date format.
-	-Hagen Telg - NOAA Affiliate</t>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	is this right?
+Reply:
+	I have 665 as the MFR10 since 20191010.  What is the 20200310 date?
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{949a4adf-7cc6-4586-b634-bfc5a0fb4cf7}" ref="C16">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	is this right? I found this empty
+</t>
       </text>
     </comment>
   </commentList>
@@ -132,13 +155,37 @@
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author/>
+    <author>tc={4259c4e5-de2f-4b9e-9beb-146c5d668cd3}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="A6">
+    <comment authorId="0" xr:uid="{4259c4e5-de2f-4b9e-9beb-146c5d668cd3}" ref="A6">
       <text>
-        <t xml:space="preserve">This is not the exact date! I just put this in in order to have a valid date format.
-	-Hagen Telg - NOAA Affiliate</t>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	This is not the exact date! I just put this in in order to have a valid date format.
+Reply:
+	688/689 were intended for Kettle Ponds but never went.  Went to Yankee for repair.  They finally sent them back a few weeks ago and FedEx lost the sensors.  Very sad to lose two new instruments.
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author>tc={ea2d1f94-e201-4456-a009-a99a41aaea9a}</author>
+  </authors>
+  <commentList>
+    <comment authorId="0" xr:uid="{ea2d1f94-e201-4456-a009-a99a41aaea9a}" ref="A6">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	This is not the exact date! I just put this in in order to have a valid date format.
+</t>
       </text>
     </comment>
   </commentList>
@@ -146,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="435">
   <si>
     <t>Instrument</t>
   </si>
@@ -1043,6 +1090,12 @@
     <t>Deploy to INL, Idaho Falls, ID site?</t>
   </si>
   <si>
+    <t>648/649</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
     <t>mfr649_20140110.xmd; mfr649_20140528.xmd</t>
   </si>
   <si>
@@ -1879,6 +1932,122 @@
 </styleSheet>
 </file>
 
+<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{b4e51d93-1f17-427b-b60b-a00675cbfc48}">
+    <Anchor>
+      <Comment id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-01-16T16:47:37.00" id="{8ae39fe6-20f3-480f-8a18-a3a52c5e17c8}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-01-16T16:47:37.00" id="{f803cbd1-4e14-4bdb-bfee-a2ed77f3bf52}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}"/>
+        </Anchor>
+        <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
+<file path=xl/documenttasks/documenttask2.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{fa62bb3c-428e-4a45-8a4e-037ce6d988df}">
+    <Anchor>
+      <Comment id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-04-27T16:25:02.00" id="{5bae1622-bc49-4014-9e93-bf0ec4da8994}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-04-27T16:25:02.00" id="{f77a5c2e-4ff4-4ab7-8ab4-e87b83354421}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}"/>
+        </Anchor>
+        <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
+<file path=xl/documenttasks/documenttask3.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{c0eefb88-fc2d-4e72-a568-39938444e14d}">
+    <Anchor>
+      <Comment id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-01-23T22:31:40.00" id="{5e43a10c-58fa-4d90-9b02-48c6fb0beed7}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-01-23T22:31:40.00" id="{e61052d6-13cb-49f6-923f-32a23f1e8810}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}"/>
+        </Anchor>
+        <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
+<file path=xl/documenttasks/documenttask4.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{edc293a1-ade2-4ef1-845c-46d9adce9cca}">
+    <Anchor>
+      <Comment id="{a6eca3d6-12b0-4885-8774-5cee5686972a}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-01-23T22:31:27.00" id="{10301cec-7067-41d7-ab99-117fccfb51b7}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{a6eca3d6-12b0-4885-8774-5cee5686972a}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-01-23T22:31:27.00" id="{2677c772-50d4-48b2-ae30-30e9617cda96}">
+        <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{a6eca3d6-12b0-4885-8774-5cee5686972a}"/>
+        </Anchor>
+        <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
+<file path=xl/documenttasks/documenttask5.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks"/>
+</file>
+
+<file path=xl/documenttasks/documenttask6.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks"/>
+</file>
+
+<file path=xl/documenttasks/documenttask7.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks"/>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -1971,6 +2140,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -1995,6 +2168,98 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <x18tc:person displayName="Hagen Telg - NOAA Affiliate" id="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" providerId="google-sheets"/>
+  <x18tc:person displayName="gary.hodges@noaa.gov" id="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" userId="gary.hodges@noaa.gov" providerId="google-sheets"/>
+  <x18tc:person displayName="Gary Hodges - NOAA Affiliate" id="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" providerId="google-sheets"/>
+</x18tc:personList>
+</file>
+
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="F4" dT="2026-01-16T16:47:37.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}" done="0">
+    <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov You mentioned below that this should be $AD23. is that correct? Why not just change it?
+Assigned to gary.hodges@noaa.gov</x18tc:text>
+    <x18tc:mentions>
+      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{e2815d5c-38df-48c2-b99f-d41cfe0cd964}" startIndex="0" length="21"/>
+    </x18tc:mentions>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="F4" dT="2026-01-16T23:24:37.00" personId="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" id="{f6e7a4e6-fc9e-48df-84ea-c61d2dee589e}" parentId="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}">
+    <x18tc:text xml:space="preserve">I just changed it.  Not sure why I didn't at the time???</x18tc:text>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="N35" dT="2026-04-27T16:25:02.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}" done="1">
+    <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov Is this correct?
+Assigned to gary.hodges@noaa.gov</x18tc:text>
+    <x18tc:mentions>
+      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{cf04b067-2ce1-46b1-84b5-a16513bf3790}" startIndex="0" length="21"/>
+    </x18tc:mentions>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="B11" dT="2026-01-23T22:31:40.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}" done="1">
+    <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov should this read "present"?
+Assigned to gary.hodges@noaa.gov</x18tc:text>
+    <x18tc:mentions>
+      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{a5628f9d-5c64-472c-8236-7e592714af82}" startIndex="0" length="21"/>
+    </x18tc:mentions>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="B9" dT="2026-01-23T22:31:27.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{a6eca3d6-12b0-4885-8774-5cee5686972a}" done="1">
+    <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov should this read "present"?
+Assigned to gary.hodges@noaa.gov</x18tc:text>
+    <x18tc:mentions>
+      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{ef1ad515-8822-4a9a-8277-979431695cf1}" startIndex="0" length="21"/>
+    </x18tc:mentions>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="C16" dT="2026-01-27T23:59:26.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{949a4adf-7cc6-4586-b634-bfc5a0fb4cf7}" done="0">
+    <x18tc:text xml:space="preserve">is this right? I found this empty</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="B16" dT="2026-01-27T23:59:08.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{3e984a89-391f-4ad1-aa44-03eb9af178d6}" done="0">
+    <x18tc:text xml:space="preserve">is this right?</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="B16" dT="2026-04-28T20:04:26.00" personId="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" id="{6b109920-7458-43f5-818d-2f947aba7276}" parentId="{3e984a89-391f-4ad1-aa44-03eb9af178d6}">
+    <x18tc:text xml:space="preserve">I have 665 as the MFR10 since 20191010.  What is the 20200310 date?</x18tc:text>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="A6" dT="2026-01-16T17:05:48.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{4259c4e5-de2f-4b9e-9beb-146c5d668cd3}" done="0">
+    <x18tc:text xml:space="preserve">This is not the exact date! I just put this in in order to have a valid date format.</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A6" dT="2026-04-28T20:05:51.00" personId="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" id="{f7016f6b-29d0-449f-ba35-d4f5eebd40d9}" parentId="{4259c4e5-de2f-4b9e-9beb-146c5d668cd3}">
+    <x18tc:text xml:space="preserve">688/689 were intended for Kettle Ponds but never went.  Went to Yankee for repair.  They finally sent them back a few weeks ago and FedEx lost the sensors.  Very sad to lose two new instruments.</x18tc:text>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="A6" dT="2026-01-16T17:53:22.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{ea2d1f94-e201-4456-a009-a99a41aaea9a}" done="0">
+    <x18tc:text xml:space="preserve">This is not the exact date! I just put this in in order to have a valid date format.</x18tc:text>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -2006,7 +2271,9 @@
     <col customWidth="1" min="1" max="6" width="10.56"/>
     <col customWidth="1" min="7" max="7" width="14.67"/>
     <col customWidth="1" min="8" max="9" width="18.56"/>
-    <col customWidth="1" min="10" max="15" width="10.56"/>
+    <col customWidth="1" min="10" max="10" width="10.56"/>
+    <col customWidth="1" min="11" max="11" width="13.67"/>
+    <col customWidth="1" min="12" max="15" width="10.56"/>
     <col customWidth="1" min="16" max="16" width="29.11"/>
     <col customWidth="1" min="17" max="27" width="10.56"/>
   </cols>
@@ -6322,8 +6589,8 @@
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -10138,9 +10405,7 @@
       <c r="A23" s="70">
         <v>43900.0</v>
       </c>
-      <c r="B23" s="71" t="s">
-        <v>198</v>
-      </c>
+      <c r="B23" s="71"/>
       <c r="C23" s="45" t="s">
         <v>108</v>
       </c>
@@ -10345,7 +10610,7 @@
     </row>
     <row r="32">
       <c r="A32" s="75">
-        <v>45589.0</v>
+        <v>45246.0</v>
       </c>
       <c r="B32" s="75">
         <v>45950.0</v>
@@ -10401,8 +10666,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="69"/>
-      <c r="B35" s="69"/>
+      <c r="A35" s="70">
+        <v>46126.0</v>
+      </c>
+      <c r="B35" s="71" t="s">
+        <v>198</v>
+      </c>
       <c r="C35" s="44" t="s">
         <v>296</v>
       </c>
@@ -10418,11 +10687,13 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
+      <c r="N35" s="44" t="s">
+        <v>298</v>
+      </c>
       <c r="O35" s="5"/>
     </row>
     <row r="36">
-      <c r="A36" s="69"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="69"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -26912,11 +27183,29 @@
       <c r="O1005" s="5"/>
     </row>
   </sheetData>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="45" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -27071,7 +27360,7 @@
         <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>190</v>
@@ -27108,7 +27397,7 @@
         <v>42565.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
@@ -27266,7 +27555,7 @@
         <v>187</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -27345,7 +27634,7 @@
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="44" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -27370,7 +27659,7 @@
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="44" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16">
@@ -27394,7 +27683,7 @@
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="44" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18">
@@ -27575,7 +27864,7 @@
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -27600,7 +27889,7 @@
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="44" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -30584,7 +30873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30714,7 +31003,7 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -30739,7 +31028,7 @@
         <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>190</v>
@@ -30754,7 +31043,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -30780,10 +31069,10 @@
       </c>
       <c r="D5" s="46"/>
       <c r="E5" s="46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6">
@@ -30812,7 +31101,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>15</v>
@@ -30830,7 +31119,7 @@
       </c>
       <c r="D8" s="46"/>
       <c r="E8" s="46" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -30844,13 +31133,13 @@
         <v>41</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E9" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -30864,13 +31153,13 @@
         <v>108</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E10" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="N10" s="46" t="s">
         <v>314</v>
-      </c>
-      <c r="N10" s="46" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -30881,14 +31170,14 @@
         <v>198</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D11" s="46"/>
       <c r="E11" s="46" t="s">
         <v>17</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12">
@@ -33859,12 +34148,12 @@
       <c r="D1000" s="46"/>
     </row>
   </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33982,7 +34271,7 @@
         <v>261</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -33999,7 +34288,7 @@
         <v>17</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
@@ -34013,7 +34302,7 @@
         <v>108</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -34027,7 +34316,7 @@
         <v>41</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -34038,13 +34327,13 @@
         <v>42644.0</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -34058,10 +34347,10 @@
         <v>108</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -34072,7 +34361,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -34084,22 +34373,22 @@
         <v>198</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E9" s="46" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34241,7 +34530,7 @@
         <v>42100.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="5" t="s">
@@ -34257,7 +34546,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -34298,7 +34587,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="2"/>
@@ -34310,7 +34599,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="44" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7">
@@ -34362,7 +34651,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -34377,7 +34666,7 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -34389,7 +34678,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
@@ -34414,11 +34703,11 @@
         <v>87</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N10" s="46"/>
       <c r="O10" s="45" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11">
@@ -34433,11 +34722,11 @@
       </c>
       <c r="D11" s="46"/>
       <c r="E11" s="54" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N11" s="46"/>
       <c r="O11" s="54" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12">
@@ -34451,14 +34740,14 @@
         <v>162</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E12" s="46" t="s">
         <v>232</v>
       </c>
       <c r="N12" s="46"/>
       <c r="O12" s="46" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13">
@@ -34475,13 +34764,13 @@
         <v>187</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O13" s="46" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -34526,7 +34815,7 @@
       </c>
       <c r="N15" s="46"/>
       <c r="O15" s="46" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16">
@@ -37516,7 +37805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -37628,7 +37917,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -37668,7 +37957,7 @@
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="2"/>
@@ -37680,7 +37969,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -37706,7 +37995,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -37743,7 +38032,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
@@ -37760,7 +38049,7 @@
         <v>232</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -37775,7 +38064,7 @@
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -37786,7 +38075,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -37804,7 +38093,7 @@
         <v>187</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -37815,7 +38104,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -37836,7 +38125,7 @@
         <v>17</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -37844,7 +38133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -37956,7 +38245,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -37996,7 +38285,7 @@
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -38008,7 +38297,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -38034,7 +38323,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -38071,7 +38360,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
@@ -38098,7 +38387,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8">
@@ -38115,7 +38404,7 @@
         <v>232</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -38130,7 +38419,7 @@
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -38141,7 +38430,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -38159,10 +38448,10 @@
         <v>187</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -38182,7 +38471,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -38190,7 +38479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -38302,7 +38591,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -38368,7 +38657,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -38383,7 +38672,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -38395,7 +38684,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -38437,10 +38726,10 @@
         <v>232</v>
       </c>
       <c r="N8" s="54" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O8" s="45" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -38457,10 +38746,10 @@
         <v>187</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N9" s="54" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -38471,13 +38760,13 @@
         <v>198</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>187</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -38488,10 +38777,10 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="54" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -38510,22 +38799,22 @@
         <v>43748.0</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C11" s="45" t="s">
         <v>108</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O11" s="45" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="90"/>
       <c r="O12" s="45" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13">
@@ -38536,11 +38825,11 @@
         <v>281</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="44" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -38561,11 +38850,11 @@
         <v>281</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="44" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -41541,7 +41830,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="45" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="45" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -41653,7 +41974,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -41692,10 +42013,10 @@
         <v>87</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
@@ -41712,7 +42033,7 @@
         <v>15</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -41727,7 +42048,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="2"/>
@@ -41739,7 +42060,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -41768,7 +42089,7 @@
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -41779,7 +42100,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -41797,7 +42118,7 @@
         <v>232</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -41811,10 +42132,10 @@
         <v>26</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11">
@@ -41828,7 +42149,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12">
@@ -41842,10 +42163,10 @@
         <v>108</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O12" s="44" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13">
@@ -41856,11 +42177,11 @@
         <v>281</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="44" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -41881,11 +42202,11 @@
         <v>281</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="44" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -41903,39 +42224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="45" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="45" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="45" t="s">
-        <v>176</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -42047,7 +42336,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -42086,10 +42375,10 @@
         <v>154</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -42104,7 +42393,7 @@
       </c>
       <c r="D5" s="50"/>
       <c r="E5" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="2"/>
@@ -42116,7 +42405,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -42131,7 +42420,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -42168,7 +42457,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -42185,7 +42474,7 @@
         <v>232</v>
       </c>
       <c r="N8" s="54" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
@@ -42202,7 +42491,7 @@
         <v>187</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -42213,11 +42502,11 @@
         <v>198</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -42228,10 +42517,10 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="44" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -42253,16 +42542,16 @@
         <v>198</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O11" s="45" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -42270,7 +42559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -42382,7 +42671,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -42421,10 +42710,10 @@
         <v>87</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5">
@@ -42451,7 +42740,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -42466,7 +42755,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="2"/>
@@ -42478,7 +42767,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -42545,7 +42834,7 @@
         <v>15</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -42560,7 +42849,7 @@
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -42571,7 +42860,7 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O10" s="5"/>
     </row>
@@ -42589,7 +42878,7 @@
         <v>232</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12">
@@ -42603,13 +42892,13 @@
         <v>26</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O12" s="45" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13">
@@ -42623,7 +42912,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14">
@@ -42637,7 +42926,7 @@
         <v>108</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
@@ -42645,19 +42934,19 @@
         <v>43748.0</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N15" s="45" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O15" s="45" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
@@ -42668,19 +42957,19 @@
         <v>198</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O16" s="45" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -42816,7 +43105,7 @@
         <v>15</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5">
@@ -42834,7 +43123,7 @@
         <v>232</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6">
@@ -42848,13 +43137,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -42872,7 +43161,7 @@
         <v>17</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
@@ -45859,7 +46148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -45998,7 +46287,7 @@
         <v>41</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>15</v>
@@ -46019,7 +46308,7 @@
         <v>232</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7">
@@ -46033,13 +46322,13 @@
         <v>41</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -46057,7 +46346,7 @@
         <v>17</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -50034,7 +50323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -50172,7 +50461,7 @@
       </c>
       <c r="N4" s="46"/>
       <c r="O4" s="46" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5">
@@ -50201,7 +50490,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>232</v>
@@ -50222,7 +50511,7 @@
         <v>187</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -50234,7 +50523,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -50273,11 +50562,11 @@
         <v>41</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N9" s="46"/>
       <c r="O9" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -50295,7 +50584,7 @@
       </c>
       <c r="N10" s="46"/>
       <c r="O10" s="46" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -54285,7 +54574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -54439,13 +54728,13 @@
         <v>41</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
@@ -54462,10 +54751,10 @@
         <v>187</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
@@ -54479,16 +54768,16 @@
         <v>41</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
@@ -54508,7 +54797,7 @@
         <v>15</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -54539,13 +54828,13 @@
         <v>162</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E10" s="46" t="s">
         <v>232</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -54568,16 +54857,16 @@
         <v>260</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O12" s="45" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -54585,7 +54874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -54708,7 +54997,7 @@
         <v>2</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -54722,13 +55011,13 @@
         <v>41</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -54745,10 +55034,10 @@
         <v>187</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
@@ -54762,13 +55051,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
@@ -54796,10 +55085,10 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
@@ -54819,7 +55108,7 @@
         <v>15</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -54833,7 +55122,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>232</v>
@@ -54847,7 +55136,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -54879,7 +55168,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12">
@@ -59829,146 +60118,6 @@
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" s="2">
-        <v>415.0</v>
-      </c>
-      <c r="I1" s="2">
-        <v>500.0</v>
-      </c>
-      <c r="J1" s="2">
-        <v>1625.0</v>
-      </c>
-      <c r="K1" s="2">
-        <v>675.0</v>
-      </c>
-      <c r="L1" s="2">
-        <v>860.0</v>
-      </c>
-      <c r="M1" s="2">
-        <v>940.0</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="64">
-        <v>44545.0</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>393</v>
-      </c>
-      <c r="O2" s="45" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="56">
-        <v>44256.0</v>
-      </c>
-      <c r="B3" s="56">
-        <v>44270.0</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="O3" s="94" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="E4" s="45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="68"/>
-      <c r="B5" s="71" t="s">
-        <v>397</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>398</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="44" t="s">
-        <v>399</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="44" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="56">
-        <v>44409.0</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>401</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -60038,14 +60187,14 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="55">
-        <v>44180.0</v>
+      <c r="A2" s="64">
+        <v>44545.0</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>393</v>
-      </c>
-      <c r="O2" s="95" t="s">
-        <v>402</v>
+        <v>395</v>
+      </c>
+      <c r="O2" s="45" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="3">
@@ -60059,33 +60208,28 @@
         <v>108</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="O3" s="96" t="s">
-        <v>403</v>
+        <v>397</v>
+      </c>
+      <c r="O3" s="94" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="4">
       <c r="E4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="45" t="s">
-        <v>404</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="68">
-        <v>44470.0</v>
-      </c>
+      <c r="A5" s="68"/>
       <c r="B5" s="71" t="s">
-        <v>281</v>
+        <v>399</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="44" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -60096,7 +60240,9 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="O5" s="44" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="56">
@@ -60106,12 +60252,12 @@
         <v>154</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -60123,161 +60269,138 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" s="2">
+        <v>415.0</v>
+      </c>
+      <c r="I1" s="2">
+        <v>500.0</v>
+      </c>
+      <c r="J1" s="2">
+        <v>1625.0</v>
+      </c>
+      <c r="K1" s="2">
+        <v>675.0</v>
+      </c>
+      <c r="L1" s="2">
+        <v>860.0</v>
+      </c>
+      <c r="M1" s="2">
+        <v>940.0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="55">
+        <v>44180.0</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="O2" s="95" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="56">
+        <v>44256.0</v>
+      </c>
+      <c r="B3" s="56">
+        <v>44270.0</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>397</v>
+      </c>
+      <c r="O3" s="96" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="58" t="s">
+    <row r="4">
+      <c r="E4" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="45" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="97"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="58" t="s">
-        <v>407</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="97"/>
+      <c r="A5" s="68">
+        <v>44470.0</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="58" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="58" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="58" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="58" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="58" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="58" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="58" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="58" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="58" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="58" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="58" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="58" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="58" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="58" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="58" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="97"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="58" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="58" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="58" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="58" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="58" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="58" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="58" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="58" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="58" t="s">
-        <v>432</v>
+      <c r="A6" s="56">
+        <v>44409.0</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -60289,7 +60412,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="3" width="10.56"/>
-    <col customWidth="1" min="4" max="4" width="28.89"/>
+    <col customWidth="1" min="4" max="4" width="36.33"/>
     <col customWidth="1" min="5" max="5" width="43.89"/>
     <col customWidth="1" min="6" max="26" width="10.56"/>
   </cols>
@@ -63437,6 +63560,172 @@
     </row>
     <row r="1000">
       <c r="D1000" s="46"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="58" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="97"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="58" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="97"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="58" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="58" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="58" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="58" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="58" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="58" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="58" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="58" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="58" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="97"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="58" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="58" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="58" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="58" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="58" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="58" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="58" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="58" t="s">
+        <v>434</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/notebooks/databases/MFRSR_History.xlsx
+++ b/notebooks/databases/MFRSR_History.xlsx
@@ -14,25 +14,24 @@
     <sheet state="visible" name="634" sheetId="9" r:id="rId12"/>
     <sheet state="visible" name="635" sheetId="10" r:id="rId13"/>
     <sheet state="visible" name="648" sheetId="11" r:id="rId14"/>
-    <sheet state="visible" name="Sheet8" sheetId="12" r:id="rId15"/>
-    <sheet state="visible" name="649" sheetId="13" r:id="rId16"/>
-    <sheet state="visible" name="650" sheetId="14" r:id="rId17"/>
-    <sheet state="visible" name="651" sheetId="15" r:id="rId18"/>
-    <sheet state="visible" name="659" sheetId="16" r:id="rId19"/>
-    <sheet state="visible" name="660" sheetId="17" r:id="rId20"/>
-    <sheet state="visible" name="661" sheetId="18" r:id="rId21"/>
-    <sheet state="visible" name="662" sheetId="19" r:id="rId22"/>
-    <sheet state="visible" name="663" sheetId="20" r:id="rId23"/>
-    <sheet state="visible" name="664" sheetId="21" r:id="rId24"/>
-    <sheet state="visible" name="665" sheetId="22" r:id="rId25"/>
-    <sheet state="visible" name="669" sheetId="23" r:id="rId26"/>
-    <sheet state="visible" name="670" sheetId="24" r:id="rId27"/>
-    <sheet state="visible" name="671" sheetId="25" r:id="rId28"/>
-    <sheet state="visible" name="672" sheetId="26" r:id="rId29"/>
-    <sheet state="visible" name="673" sheetId="27" r:id="rId30"/>
-    <sheet state="visible" name="688" sheetId="28" r:id="rId31"/>
-    <sheet state="visible" name="689" sheetId="29" r:id="rId32"/>
-    <sheet state="visible" name="Notes" sheetId="30" r:id="rId33"/>
+    <sheet state="visible" name="649" sheetId="12" r:id="rId15"/>
+    <sheet state="visible" name="650" sheetId="13" r:id="rId16"/>
+    <sheet state="visible" name="651" sheetId="14" r:id="rId17"/>
+    <sheet state="visible" name="659" sheetId="15" r:id="rId18"/>
+    <sheet state="visible" name="660" sheetId="16" r:id="rId19"/>
+    <sheet state="visible" name="661" sheetId="17" r:id="rId20"/>
+    <sheet state="visible" name="662" sheetId="18" r:id="rId21"/>
+    <sheet state="visible" name="663" sheetId="19" r:id="rId22"/>
+    <sheet state="visible" name="664" sheetId="20" r:id="rId23"/>
+    <sheet state="visible" name="665" sheetId="21" r:id="rId24"/>
+    <sheet state="visible" name="669" sheetId="22" r:id="rId25"/>
+    <sheet state="visible" name="670" sheetId="23" r:id="rId26"/>
+    <sheet state="visible" name="671" sheetId="24" r:id="rId27"/>
+    <sheet state="visible" name="672" sheetId="25" r:id="rId28"/>
+    <sheet state="visible" name="673" sheetId="26" r:id="rId29"/>
+    <sheet state="visible" name="688" sheetId="27" r:id="rId30"/>
+    <sheet state="visible" name="689" sheetId="28" r:id="rId31"/>
+    <sheet state="visible" name="Notes" sheetId="29" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -42,10 +41,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={5af9e62f-a87f-4f00-a2fd-3bc89eae7088}</author>
+    <author>tc={86d95a78-65c2-4747-8f31-20b7bddf2c93}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}" ref="F4">
+    <comment authorId="0" xr:uid="{86d95a78-65c2-4747-8f31-20b7bddf2c93}" ref="F4">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -64,10 +63,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={afa8b239-4954-4803-8f0e-7fe2dbc39426}</author>
+    <author>tc={aae6ce08-58da-4d4e-a1f6-8ff7efb551d3}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{afa8b239-4954-4803-8f0e-7fe2dbc39426}" ref="N35">
+    <comment authorId="0" xr:uid="{aae6ce08-58da-4d4e-a1f6-8ff7efb551d3}" ref="N35">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,10 +83,10 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={474bdb03-b157-42c7-bd2d-54363d7a8a2a}</author>
+    <author>tc={0088307a-d4b0-4d9d-95d3-7e27ac7ee09e}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}" ref="B11">
+    <comment authorId="0" xr:uid="{0088307a-d4b0-4d9d-95d3-7e27ac7ee09e}" ref="B11">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -104,10 +103,10 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={a6eca3d6-12b0-4885-8774-5cee5686972a}</author>
+    <author>tc={34c0919b-8714-4c44-be85-854a0af7c5e7}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{a6eca3d6-12b0-4885-8774-5cee5686972a}" ref="B9">
+    <comment authorId="0" xr:uid="{34c0919b-8714-4c44-be85-854a0af7c5e7}" ref="B9">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -124,11 +123,11 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={3e984a89-391f-4ad1-aa44-03eb9af178d6}</author>
-    <author>tc={949a4adf-7cc6-4586-b634-bfc5a0fb4cf7}</author>
+    <author>tc={99cb9ae2-7ca5-465c-8aab-eae24c24eb8d}</author>
+    <author>tc={caa1e444-de2e-4000-8a2f-41c83d39d059}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{3e984a89-391f-4ad1-aa44-03eb9af178d6}" ref="B16">
+    <comment authorId="0" xr:uid="{99cb9ae2-7ca5-465c-8aab-eae24c24eb8d}" ref="B16">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -139,7 +138,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{949a4adf-7cc6-4586-b634-bfc5a0fb4cf7}" ref="C16">
+    <comment authorId="1" xr:uid="{caa1e444-de2e-4000-8a2f-41c83d39d059}" ref="C16">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -155,10 +154,10 @@
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={4259c4e5-de2f-4b9e-9beb-146c5d668cd3}</author>
+    <author>tc={9a045339-525b-49b4-bab6-938066e7ded8}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{4259c4e5-de2f-4b9e-9beb-146c5d668cd3}" ref="A6">
+    <comment authorId="0" xr:uid="{9a045339-525b-49b4-bab6-938066e7ded8}" ref="A6">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -176,10 +175,10 @@
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={ea2d1f94-e201-4456-a009-a99a41aaea9a}</author>
+    <author>tc={e151c161-cbc2-4700-b265-8a44464eb67c}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{ea2d1f94-e201-4456-a009-a99a41aaea9a}" ref="A6">
+    <comment authorId="0" xr:uid="{e151c161-cbc2-4700-b265-8a44464eb67c}" ref="A6">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -193,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="434">
   <si>
     <t>Instrument</t>
   </si>
@@ -1078,10 +1077,10 @@
     <t>Characterized in CUCF, wet</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>DAV</t>
   </si>
   <si>
-    <t>Deploy to PMOD FRC Campaign</t>
+    <t>Deploy to PMOD FRC Campaign in Davos</t>
   </si>
   <si>
     <t>INL</t>
@@ -1091,9 +1090,6 @@
   </si>
   <si>
     <t>648/649</t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t>mfr649_20140110.xmd; mfr649_20140528.xmd</t>
@@ -1641,7 +1637,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1867,9 +1863,6 @@
     <xf borderId="0" fillId="9" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1934,22 +1927,22 @@
 
 <file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{b4e51d93-1f17-427b-b60b-a00675cbfc48}">
+  <Task id="{41acbb3e-0a4c-4754-811a-15c9187adb6c}">
     <Anchor>
-      <Comment id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}"/>
+      <Comment id="{86d95a78-65c2-4747-8f31-20b7bddf2c93}"/>
     </Anchor>
     <History>
-      <Event time="2026-01-16T16:47:37.00" id="{8ae39fe6-20f3-480f-8a18-a3a52c5e17c8}">
+      <Event time="2026-01-16T16:47:37.00" id="{6270d8e3-e1a1-4653-995c-7abe64cb6615}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}"/>
+          <Comment id="{86d95a78-65c2-4747-8f31-20b7bddf2c93}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2026-01-16T16:47:37.00" id="{f803cbd1-4e14-4bdb-bfee-a2ed77f3bf52}">
+      <Event time="2026-01-16T16:47:37.00" id="{405ab421-f0e6-49e3-b278-de14b51f3f90}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}"/>
+          <Comment id="{86d95a78-65c2-4747-8f31-20b7bddf2c93}"/>
         </Anchor>
         <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
       </Event>
@@ -1960,22 +1953,22 @@
 
 <file path=xl/documenttasks/documenttask2.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{fa62bb3c-428e-4a45-8a4e-037ce6d988df}">
+  <Task id="{e2ba0288-bb29-4d10-ac64-0d09e557244b}">
     <Anchor>
-      <Comment id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}"/>
+      <Comment id="{aae6ce08-58da-4d4e-a1f6-8ff7efb551d3}"/>
     </Anchor>
     <History>
-      <Event time="2026-04-27T16:25:02.00" id="{5bae1622-bc49-4014-9e93-bf0ec4da8994}">
+      <Event time="2026-04-27T16:25:02.00" id="{e82a709a-3fe4-4b01-8ff4-ce00f06dff61}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}"/>
+          <Comment id="{aae6ce08-58da-4d4e-a1f6-8ff7efb551d3}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2026-04-27T16:25:02.00" id="{f77a5c2e-4ff4-4ab7-8ab4-e87b83354421}">
+      <Event time="2026-04-27T16:25:02.00" id="{9038bc9b-8eb4-4e6c-a552-5a9b9fc79a77}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}"/>
+          <Comment id="{aae6ce08-58da-4d4e-a1f6-8ff7efb551d3}"/>
         </Anchor>
         <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
       </Event>
@@ -1986,22 +1979,22 @@
 
 <file path=xl/documenttasks/documenttask3.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{c0eefb88-fc2d-4e72-a568-39938444e14d}">
+  <Task id="{b818d989-9869-4194-92bf-d60fa27b5320}">
     <Anchor>
-      <Comment id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}"/>
+      <Comment id="{0088307a-d4b0-4d9d-95d3-7e27ac7ee09e}"/>
     </Anchor>
     <History>
-      <Event time="2026-01-23T22:31:40.00" id="{5e43a10c-58fa-4d90-9b02-48c6fb0beed7}">
+      <Event time="2026-01-23T22:31:40.00" id="{4e753ddb-c354-4a90-9618-7268bb8e9b12}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}"/>
+          <Comment id="{0088307a-d4b0-4d9d-95d3-7e27ac7ee09e}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2026-01-23T22:31:40.00" id="{e61052d6-13cb-49f6-923f-32a23f1e8810}">
+      <Event time="2026-01-23T22:31:40.00" id="{9214b246-8362-449d-877e-23b2f0ced9fd}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}"/>
+          <Comment id="{0088307a-d4b0-4d9d-95d3-7e27ac7ee09e}"/>
         </Anchor>
         <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
       </Event>
@@ -2012,22 +2005,22 @@
 
 <file path=xl/documenttasks/documenttask4.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{edc293a1-ade2-4ef1-845c-46d9adce9cca}">
+  <Task id="{d224f8f1-b591-4a89-9fb3-a15359c12ebb}">
     <Anchor>
-      <Comment id="{a6eca3d6-12b0-4885-8774-5cee5686972a}"/>
+      <Comment id="{34c0919b-8714-4c44-be85-854a0af7c5e7}"/>
     </Anchor>
     <History>
-      <Event time="2026-01-23T22:31:27.00" id="{10301cec-7067-41d7-ab99-117fccfb51b7}">
+      <Event time="2026-01-23T22:31:27.00" id="{fe645440-3c39-418e-b457-8d0023408d8b}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{a6eca3d6-12b0-4885-8774-5cee5686972a}"/>
+          <Comment id="{34c0919b-8714-4c44-be85-854a0af7c5e7}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2026-01-23T22:31:27.00" id="{2677c772-50d4-48b2-ae30-30e9617cda96}">
+      <Event time="2026-01-23T22:31:27.00" id="{21fd8c78-926d-41c5-9c45-dbe7476a3db1}">
         <Attribution userId="placeholder@email.com" userName="Hagen Telg - NOAA Affiliate" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{a6eca3d6-12b0-4885-8774-5cee5686972a}"/>
+          <Comment id="{34c0919b-8714-4c44-be85-854a0af7c5e7}"/>
         </Anchor>
         <Assign userId="gary.hodges@noaa.gov" userName="gary.hodges@noaa.gov" userProvider="google-sheets"/>
       </Event>
@@ -2140,10 +2133,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -2170,22 +2159,22 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Hagen Telg - NOAA Affiliate" id="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" providerId="google-sheets"/>
-  <x18tc:person displayName="gary.hodges@noaa.gov" id="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" userId="gary.hodges@noaa.gov" providerId="google-sheets"/>
-  <x18tc:person displayName="Gary Hodges - NOAA Affiliate" id="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" providerId="google-sheets"/>
+  <x18tc:person displayName="Hagen Telg - NOAA Affiliate" id="{14e3be25-f152-4389-b714-781eab9b1d48}" providerId="google-sheets"/>
+  <x18tc:person displayName="gary.hodges@noaa.gov" id="{79cafcd3-a21a-47c4-b316-4874345f32bc}" userId="gary.hodges@noaa.gov" providerId="google-sheets"/>
+  <x18tc:person displayName="Gary Hodges - NOAA Affiliate" id="{a3dabea9-785d-4e17-877e-e8f00ffde893}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="F4" dT="2026-01-16T16:47:37.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}" done="0">
+  <x18tc:threadedComment ref="F4" dT="2026-01-16T16:47:37.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{86d95a78-65c2-4747-8f31-20b7bddf2c93}" done="0">
     <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov You mentioned below that this should be $AD23. is that correct? Why not just change it?
 Assigned to gary.hodges@noaa.gov</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{e2815d5c-38df-48c2-b99f-d41cfe0cd964}" startIndex="0" length="21"/>
+      <x18tc:mention mentionpersonId="{79cafcd3-a21a-47c4-b316-4874345f32bc}" mentionId="{e52d8395-9a2a-4791-9be8-ad33370f1629}" startIndex="0" length="21"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F4" dT="2026-01-16T23:24:37.00" personId="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" id="{f6e7a4e6-fc9e-48df-84ea-c61d2dee589e}" parentId="{5af9e62f-a87f-4f00-a2fd-3bc89eae7088}">
+  <x18tc:threadedComment ref="F4" dT="2026-01-16T23:24:37.00" personId="{a3dabea9-785d-4e17-877e-e8f00ffde893}" id="{2d794a52-27d4-43cd-96b9-587deaa75504}" parentId="{86d95a78-65c2-4747-8f31-20b7bddf2c93}">
     <x18tc:text xml:space="preserve">I just changed it.  Not sure why I didn't at the time???</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2193,11 +2182,11 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="N35" dT="2026-04-27T16:25:02.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{afa8b239-4954-4803-8f0e-7fe2dbc39426}" done="1">
+  <x18tc:threadedComment ref="N35" dT="2026-04-27T16:25:02.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{aae6ce08-58da-4d4e-a1f6-8ff7efb551d3}" done="1">
     <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov Is this correct?
 Assigned to gary.hodges@noaa.gov</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{cf04b067-2ce1-46b1-84b5-a16513bf3790}" startIndex="0" length="21"/>
+      <x18tc:mention mentionpersonId="{79cafcd3-a21a-47c4-b316-4874345f32bc}" mentionId="{273759a1-fdb0-48a4-ac2d-9050fe2931fe}" startIndex="0" length="21"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2205,11 +2194,11 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B11" dT="2026-01-23T22:31:40.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{474bdb03-b157-42c7-bd2d-54363d7a8a2a}" done="1">
+  <x18tc:threadedComment ref="B11" dT="2026-01-23T22:31:40.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{0088307a-d4b0-4d9d-95d3-7e27ac7ee09e}" done="1">
     <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov should this read "present"?
 Assigned to gary.hodges@noaa.gov</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{a5628f9d-5c64-472c-8236-7e592714af82}" startIndex="0" length="21"/>
+      <x18tc:mention mentionpersonId="{79cafcd3-a21a-47c4-b316-4874345f32bc}" mentionId="{cb0adedf-8a38-43db-9901-fa148229a98d}" startIndex="0" length="21"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2217,11 +2206,11 @@
 
 <file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B9" dT="2026-01-23T22:31:27.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{a6eca3d6-12b0-4885-8774-5cee5686972a}" done="1">
+  <x18tc:threadedComment ref="B9" dT="2026-01-23T22:31:27.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{34c0919b-8714-4c44-be85-854a0af7c5e7}" done="1">
     <x18tc:text xml:space="preserve">@gary.hodges@noaa.gov should this read "present"?
 Assigned to gary.hodges@noaa.gov</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{4db97f81-caa7-4cfe-9c2f-adda9c0cf199}" mentionId="{ef1ad515-8822-4a9a-8277-979431695cf1}" startIndex="0" length="21"/>
+      <x18tc:mention mentionpersonId="{79cafcd3-a21a-47c4-b316-4874345f32bc}" mentionId="{6afbbbfd-43d2-4226-a15e-b241560831a6}" startIndex="0" length="21"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2229,13 +2218,13 @@
 
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="C16" dT="2026-01-27T23:59:26.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{949a4adf-7cc6-4586-b634-bfc5a0fb4cf7}" done="0">
+  <x18tc:threadedComment ref="C16" dT="2026-01-27T23:59:26.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{caa1e444-de2e-4000-8a2f-41c83d39d059}" done="0">
     <x18tc:text xml:space="preserve">is this right? I found this empty</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B16" dT="2026-01-27T23:59:08.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{3e984a89-391f-4ad1-aa44-03eb9af178d6}" done="0">
+  <x18tc:threadedComment ref="B16" dT="2026-01-27T23:59:08.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{99cb9ae2-7ca5-465c-8aab-eae24c24eb8d}" done="0">
     <x18tc:text xml:space="preserve">is this right?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B16" dT="2026-04-28T20:04:26.00" personId="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" id="{6b109920-7458-43f5-818d-2f947aba7276}" parentId="{3e984a89-391f-4ad1-aa44-03eb9af178d6}">
+  <x18tc:threadedComment ref="B16" dT="2026-04-28T20:04:26.00" personId="{a3dabea9-785d-4e17-877e-e8f00ffde893}" id="{2e218cc6-7293-46ce-90ce-89885e6922d3}" parentId="{99cb9ae2-7ca5-465c-8aab-eae24c24eb8d}">
     <x18tc:text xml:space="preserve">I have 665 as the MFR10 since 20191010.  What is the 20200310 date?</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2243,10 +2232,10 @@
 
 <file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A6" dT="2026-01-16T17:05:48.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{4259c4e5-de2f-4b9e-9beb-146c5d668cd3}" done="0">
+  <x18tc:threadedComment ref="A6" dT="2026-01-16T17:05:48.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{9a045339-525b-49b4-bab6-938066e7ded8}" done="0">
     <x18tc:text xml:space="preserve">This is not the exact date! I just put this in in order to have a valid date format.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A6" dT="2026-04-28T20:05:51.00" personId="{4fa31c7b-fac6-4888-8c09-ecd10ef7ad00}" id="{f7016f6b-29d0-449f-ba35-d4f5eebd40d9}" parentId="{4259c4e5-de2f-4b9e-9beb-146c5d668cd3}">
+  <x18tc:threadedComment ref="A6" dT="2026-04-28T20:05:51.00" personId="{a3dabea9-785d-4e17-877e-e8f00ffde893}" id="{d4919bf5-d2e2-4151-9011-bc03d099fc7f}" parentId="{9a045339-525b-49b4-bab6-938066e7ded8}">
     <x18tc:text xml:space="preserve">688/689 were intended for Kettle Ponds but never went.  Went to Yankee for repair.  They finally sent them back a few weeks ago and FedEx lost the sensors.  Very sad to lose two new instruments.</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2254,7 +2243,7 @@
 
 <file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A6" dT="2026-01-16T17:53:22.00" personId="{73bc003e-fed8-451b-a3b7-86bdeb2c2653}" id="{ea2d1f94-e201-4456-a009-a99a41aaea9a}" done="0">
+  <x18tc:threadedComment ref="A6" dT="2026-01-16T17:53:22.00" personId="{14e3be25-f152-4389-b714-781eab9b1d48}" id="{e151c161-cbc2-4700-b265-8a44464eb67c}" done="0">
     <x18tc:text xml:space="preserve">This is not the exact date! I just put this in in order to have a valid date format.</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -10649,18 +10638,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="77">
+      <c r="A34" s="56">
         <v>45920.0</v>
       </c>
-      <c r="B34" s="76">
-        <v>45940.0</v>
+      <c r="B34" s="55">
+        <v>45952.0</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="D34" s="54" t="s">
         <v>294</v>
       </c>
+      <c r="D34" s="54"/>
       <c r="E34" s="45" t="s">
         <v>295</v>
       </c>
@@ -27194,23 +27181,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="45" t="s">
-        <v>299</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="3" width="10.56"/>
     <col customWidth="1" min="4" max="4" width="20.78"/>
@@ -27360,7 +27330,7 @@
         <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>190</v>
@@ -27397,7 +27367,7 @@
         <v>42565.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
@@ -27555,7 +27525,7 @@
         <v>187</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -27634,7 +27604,7 @@
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -27659,7 +27629,7 @@
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
@@ -27683,7 +27653,7 @@
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18">
@@ -27817,42 +27787,42 @@
       <c r="O23" s="5"/>
     </row>
     <row r="24">
-      <c r="A24" s="78">
+      <c r="A24" s="77">
         <v>44454.0</v>
       </c>
       <c r="B24" s="74" t="s">
         <v>281</v>
       </c>
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="78" t="s">
         <v>286</v>
       </c>
-      <c r="D24" s="79" t="s">
+      <c r="D24" s="78" t="s">
         <v>287</v>
       </c>
-      <c r="E24" s="79" t="s">
+      <c r="E24" s="78" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="81"/>
-      <c r="T24" s="81"/>
-      <c r="U24" s="81"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="81"/>
-      <c r="X24" s="81"/>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="81"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="80"/>
+      <c r="T24" s="80"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="80"/>
+      <c r="W24" s="80"/>
+      <c r="X24" s="80"/>
+      <c r="Y24" s="80"/>
+      <c r="Z24" s="80"/>
     </row>
     <row r="25">
       <c r="A25" s="68">
@@ -27864,7 +27834,7 @@
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -27889,7 +27859,7 @@
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -27922,14 +27892,12 @@
         <v>45920.0</v>
       </c>
       <c r="B28" s="55">
-        <v>45940.0</v>
+        <v>45952.0</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="D28" s="54" t="s">
         <v>294</v>
       </c>
+      <c r="D28" s="54"/>
       <c r="E28" s="45" t="s">
         <v>295</v>
       </c>
@@ -30873,7 +30841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31003,7 +30971,7 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -31028,7 +30996,7 @@
         <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>190</v>
@@ -31043,7 +31011,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -31069,10 +31037,10 @@
       </c>
       <c r="D5" s="46"/>
       <c r="E5" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="N5" s="46" t="s">
         <v>310</v>
-      </c>
-      <c r="N5" s="46" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="6">
@@ -31101,7 +31069,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>15</v>
@@ -31119,7 +31087,7 @@
       </c>
       <c r="D8" s="46"/>
       <c r="E8" s="46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -31133,13 +31101,13 @@
         <v>41</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E9" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -31153,31 +31121,31 @@
         <v>108</v>
       </c>
       <c r="D10" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="E10" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="E10" s="46" t="s">
-        <v>316</v>
-      </c>
       <c r="N10" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="63">
         <v>42661.0</v>
       </c>
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="81" t="s">
         <v>198</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D11" s="46"/>
       <c r="E11" s="46" t="s">
         <v>17</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12">
@@ -34153,7 +34121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34271,7 +34239,7 @@
         <v>261</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -34288,7 +34256,7 @@
         <v>17</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5">
@@ -34302,7 +34270,7 @@
         <v>108</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -34316,7 +34284,7 @@
         <v>41</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -34327,13 +34295,13 @@
         <v>42644.0</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -34347,10 +34315,10 @@
         <v>108</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -34361,7 +34329,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -34369,17 +34337,17 @@
       <c r="A9" s="63">
         <v>42660.0</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="81" t="s">
         <v>198</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E9" s="46" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -34388,7 +34356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34530,7 +34498,7 @@
         <v>42100.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="5" t="s">
@@ -34546,7 +34514,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -34587,7 +34555,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="2"/>
@@ -34599,7 +34567,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7">
@@ -34651,7 +34619,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -34666,7 +34634,7 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -34678,7 +34646,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
@@ -34696,18 +34664,18 @@
       <c r="A10" s="51">
         <v>42227.0</v>
       </c>
-      <c r="B10" s="83">
+      <c r="B10" s="82">
         <v>42249.0</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>87</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N10" s="46"/>
       <c r="O10" s="45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11">
@@ -34722,11 +34690,11 @@
       </c>
       <c r="D11" s="46"/>
       <c r="E11" s="54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N11" s="46"/>
       <c r="O11" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12">
@@ -34740,14 +34708,14 @@
         <v>162</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E12" s="46" t="s">
         <v>232</v>
       </c>
       <c r="N12" s="46"/>
       <c r="O12" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13">
@@ -34764,13 +34732,13 @@
         <v>187</v>
       </c>
       <c r="E13" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="N13" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="N13" s="46" t="s">
+      <c r="O13" s="46" t="s">
         <v>336</v>
-      </c>
-      <c r="O13" s="46" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -34780,7 +34748,7 @@
       <c r="B14" s="51">
         <v>42527.0</v>
       </c>
-      <c r="C14" s="84" t="s">
+      <c r="C14" s="83" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -34815,7 +34783,7 @@
       </c>
       <c r="N15" s="46"/>
       <c r="O15" s="46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16">
@@ -37805,7 +37773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -37917,7 +37885,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -37957,7 +37925,7 @@
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="2"/>
@@ -37969,7 +37937,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -37995,7 +37963,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -38032,7 +38000,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7">
@@ -38049,7 +38017,7 @@
         <v>232</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -38064,7 +38032,7 @@
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -38075,7 +38043,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -38093,7 +38061,7 @@
         <v>187</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -38104,7 +38072,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -38125,7 +38093,7 @@
         <v>17</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -38133,7 +38101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -38245,7 +38213,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -38285,7 +38253,7 @@
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -38297,7 +38265,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -38323,7 +38291,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -38360,7 +38328,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7">
@@ -38387,7 +38355,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8">
@@ -38404,7 +38372,7 @@
         <v>232</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -38419,7 +38387,7 @@
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -38430,7 +38398,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -38448,10 +38416,10 @@
         <v>187</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -38471,7 +38439,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -38479,7 +38447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -38490,7 +38458,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>177</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -38548,7 +38516,7 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="86">
+      <c r="A2" s="85">
         <v>41680.0</v>
       </c>
       <c r="B2" s="51">
@@ -38584,14 +38552,14 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="87">
+      <c r="A3" s="86">
         <v>42085.0</v>
       </c>
       <c r="B3" s="51">
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -38620,7 +38588,7 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="87">
+      <c r="A4" s="86">
         <v>42124.0</v>
       </c>
       <c r="B4" s="51">
@@ -38634,7 +38602,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="86">
+      <c r="A5" s="85">
         <v>42126.0</v>
       </c>
       <c r="B5" s="51">
@@ -38657,11 +38625,11 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="88">
+      <c r="A6" s="87">
         <v>42130.0</v>
       </c>
       <c r="B6" s="51">
@@ -38672,7 +38640,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -38684,7 +38652,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -38699,7 +38667,7 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="87">
+      <c r="A7" s="86">
         <v>42156.0</v>
       </c>
       <c r="B7" s="51">
@@ -38713,7 +38681,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86">
+      <c r="A8" s="85">
         <v>42184.0</v>
       </c>
       <c r="B8" s="51">
@@ -38726,14 +38694,14 @@
         <v>232</v>
       </c>
       <c r="N8" s="54" t="s">
+        <v>343</v>
+      </c>
+      <c r="O8" s="45" t="s">
         <v>344</v>
       </c>
-      <c r="O8" s="45" t="s">
-        <v>345</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="86">
+      <c r="A9" s="85">
         <v>42185.0</v>
       </c>
       <c r="B9" s="51">
@@ -38746,27 +38714,27 @@
         <v>187</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N9" s="54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="87">
+      <c r="A10" s="86">
         <v>42200.0</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>198</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>187</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -38777,10 +38745,10 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -38795,41 +38763,41 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="89">
+      <c r="A11" s="88">
         <v>43748.0</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C11" s="45" t="s">
         <v>108</v>
       </c>
       <c r="E11" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="O11" s="45" t="s">
         <v>349</v>
       </c>
-      <c r="O11" s="45" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="89"/>
+      <c r="O12" s="45" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="90"/>
-      <c r="O12" s="45" t="s">
+    <row r="13">
+      <c r="A13" s="90">
+        <v>44470.0</v>
+      </c>
+      <c r="B13" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="44" t="s">
         <v>351</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="91">
-        <v>44470.0</v>
-      </c>
-      <c r="B13" s="92" t="s">
-        <v>281</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>352</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="44" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -38843,18 +38811,18 @@
       <c r="O13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="91">
+      <c r="A14" s="90">
         <v>45597.0</v>
       </c>
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="91" t="s">
         <v>281</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="44" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -38868,3001 +38836,2969 @@
       <c r="O14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="90"/>
+      <c r="A15" s="89"/>
     </row>
     <row r="16">
-      <c r="A16" s="90"/>
+      <c r="A16" s="89"/>
     </row>
     <row r="17">
-      <c r="A17" s="90"/>
+      <c r="A17" s="89"/>
     </row>
     <row r="18">
-      <c r="A18" s="90"/>
+      <c r="A18" s="89"/>
     </row>
     <row r="19">
-      <c r="A19" s="90"/>
+      <c r="A19" s="89"/>
     </row>
     <row r="20">
-      <c r="A20" s="90"/>
+      <c r="A20" s="89"/>
     </row>
     <row r="21">
-      <c r="A21" s="90"/>
+      <c r="A21" s="89"/>
     </row>
     <row r="22">
-      <c r="A22" s="90"/>
+      <c r="A22" s="89"/>
     </row>
     <row r="23">
-      <c r="A23" s="90"/>
+      <c r="A23" s="89"/>
     </row>
     <row r="24">
-      <c r="A24" s="90"/>
+      <c r="A24" s="89"/>
     </row>
     <row r="25">
-      <c r="A25" s="90"/>
+      <c r="A25" s="89"/>
     </row>
     <row r="26">
-      <c r="A26" s="90"/>
+      <c r="A26" s="89"/>
     </row>
     <row r="27">
-      <c r="A27" s="90"/>
+      <c r="A27" s="89"/>
     </row>
     <row r="28">
-      <c r="A28" s="90"/>
+      <c r="A28" s="89"/>
     </row>
     <row r="29">
-      <c r="A29" s="90"/>
+      <c r="A29" s="89"/>
     </row>
     <row r="30">
-      <c r="A30" s="90"/>
+      <c r="A30" s="89"/>
     </row>
     <row r="31">
-      <c r="A31" s="90"/>
+      <c r="A31" s="89"/>
     </row>
     <row r="32">
-      <c r="A32" s="90"/>
+      <c r="A32" s="89"/>
     </row>
     <row r="33">
-      <c r="A33" s="90"/>
+      <c r="A33" s="89"/>
     </row>
     <row r="34">
-      <c r="A34" s="90"/>
+      <c r="A34" s="89"/>
     </row>
     <row r="35">
-      <c r="A35" s="90"/>
+      <c r="A35" s="89"/>
     </row>
     <row r="36">
-      <c r="A36" s="90"/>
+      <c r="A36" s="89"/>
     </row>
     <row r="37">
-      <c r="A37" s="90"/>
+      <c r="A37" s="89"/>
     </row>
     <row r="38">
-      <c r="A38" s="90"/>
+      <c r="A38" s="89"/>
     </row>
     <row r="39">
-      <c r="A39" s="90"/>
+      <c r="A39" s="89"/>
     </row>
     <row r="40">
-      <c r="A40" s="90"/>
+      <c r="A40" s="89"/>
     </row>
     <row r="41">
-      <c r="A41" s="90"/>
+      <c r="A41" s="89"/>
     </row>
     <row r="42">
-      <c r="A42" s="90"/>
+      <c r="A42" s="89"/>
     </row>
     <row r="43">
-      <c r="A43" s="90"/>
+      <c r="A43" s="89"/>
     </row>
     <row r="44">
-      <c r="A44" s="90"/>
+      <c r="A44" s="89"/>
     </row>
     <row r="45">
-      <c r="A45" s="90"/>
+      <c r="A45" s="89"/>
     </row>
     <row r="46">
-      <c r="A46" s="90"/>
+      <c r="A46" s="89"/>
     </row>
     <row r="47">
-      <c r="A47" s="90"/>
+      <c r="A47" s="89"/>
     </row>
     <row r="48">
-      <c r="A48" s="90"/>
+      <c r="A48" s="89"/>
     </row>
     <row r="49">
-      <c r="A49" s="90"/>
+      <c r="A49" s="89"/>
     </row>
     <row r="50">
-      <c r="A50" s="90"/>
+      <c r="A50" s="89"/>
     </row>
     <row r="51">
-      <c r="A51" s="90"/>
+      <c r="A51" s="89"/>
     </row>
     <row r="52">
-      <c r="A52" s="90"/>
+      <c r="A52" s="89"/>
     </row>
     <row r="53">
-      <c r="A53" s="90"/>
+      <c r="A53" s="89"/>
     </row>
     <row r="54">
-      <c r="A54" s="90"/>
+      <c r="A54" s="89"/>
     </row>
     <row r="55">
-      <c r="A55" s="90"/>
+      <c r="A55" s="89"/>
     </row>
     <row r="56">
-      <c r="A56" s="90"/>
+      <c r="A56" s="89"/>
     </row>
     <row r="57">
-      <c r="A57" s="90"/>
+      <c r="A57" s="89"/>
     </row>
     <row r="58">
-      <c r="A58" s="90"/>
+      <c r="A58" s="89"/>
     </row>
     <row r="59">
-      <c r="A59" s="90"/>
+      <c r="A59" s="89"/>
     </row>
     <row r="60">
-      <c r="A60" s="90"/>
+      <c r="A60" s="89"/>
     </row>
     <row r="61">
-      <c r="A61" s="90"/>
+      <c r="A61" s="89"/>
     </row>
     <row r="62">
-      <c r="A62" s="90"/>
+      <c r="A62" s="89"/>
     </row>
     <row r="63">
-      <c r="A63" s="90"/>
+      <c r="A63" s="89"/>
     </row>
     <row r="64">
-      <c r="A64" s="90"/>
+      <c r="A64" s="89"/>
     </row>
     <row r="65">
-      <c r="A65" s="90"/>
+      <c r="A65" s="89"/>
     </row>
     <row r="66">
-      <c r="A66" s="90"/>
+      <c r="A66" s="89"/>
     </row>
     <row r="67">
-      <c r="A67" s="90"/>
+      <c r="A67" s="89"/>
     </row>
     <row r="68">
-      <c r="A68" s="90"/>
+      <c r="A68" s="89"/>
     </row>
     <row r="69">
-      <c r="A69" s="90"/>
+      <c r="A69" s="89"/>
     </row>
     <row r="70">
-      <c r="A70" s="90"/>
+      <c r="A70" s="89"/>
     </row>
     <row r="71">
-      <c r="A71" s="90"/>
+      <c r="A71" s="89"/>
     </row>
     <row r="72">
-      <c r="A72" s="90"/>
+      <c r="A72" s="89"/>
     </row>
     <row r="73">
-      <c r="A73" s="90"/>
+      <c r="A73" s="89"/>
     </row>
     <row r="74">
-      <c r="A74" s="90"/>
+      <c r="A74" s="89"/>
     </row>
     <row r="75">
-      <c r="A75" s="90"/>
+      <c r="A75" s="89"/>
     </row>
     <row r="76">
-      <c r="A76" s="90"/>
+      <c r="A76" s="89"/>
     </row>
     <row r="77">
-      <c r="A77" s="90"/>
+      <c r="A77" s="89"/>
     </row>
     <row r="78">
-      <c r="A78" s="90"/>
+      <c r="A78" s="89"/>
     </row>
     <row r="79">
-      <c r="A79" s="90"/>
+      <c r="A79" s="89"/>
     </row>
     <row r="80">
-      <c r="A80" s="90"/>
+      <c r="A80" s="89"/>
     </row>
     <row r="81">
-      <c r="A81" s="90"/>
+      <c r="A81" s="89"/>
     </row>
     <row r="82">
-      <c r="A82" s="90"/>
+      <c r="A82" s="89"/>
     </row>
     <row r="83">
-      <c r="A83" s="90"/>
+      <c r="A83" s="89"/>
     </row>
     <row r="84">
-      <c r="A84" s="90"/>
+      <c r="A84" s="89"/>
     </row>
     <row r="85">
-      <c r="A85" s="90"/>
+      <c r="A85" s="89"/>
     </row>
     <row r="86">
-      <c r="A86" s="90"/>
+      <c r="A86" s="89"/>
     </row>
     <row r="87">
-      <c r="A87" s="90"/>
+      <c r="A87" s="89"/>
     </row>
     <row r="88">
-      <c r="A88" s="90"/>
+      <c r="A88" s="89"/>
     </row>
     <row r="89">
-      <c r="A89" s="90"/>
+      <c r="A89" s="89"/>
     </row>
     <row r="90">
-      <c r="A90" s="90"/>
+      <c r="A90" s="89"/>
     </row>
     <row r="91">
-      <c r="A91" s="90"/>
+      <c r="A91" s="89"/>
     </row>
     <row r="92">
-      <c r="A92" s="90"/>
+      <c r="A92" s="89"/>
     </row>
     <row r="93">
-      <c r="A93" s="90"/>
+      <c r="A93" s="89"/>
     </row>
     <row r="94">
-      <c r="A94" s="90"/>
+      <c r="A94" s="89"/>
     </row>
     <row r="95">
-      <c r="A95" s="90"/>
+      <c r="A95" s="89"/>
     </row>
     <row r="96">
-      <c r="A96" s="90"/>
+      <c r="A96" s="89"/>
     </row>
     <row r="97">
-      <c r="A97" s="90"/>
+      <c r="A97" s="89"/>
     </row>
     <row r="98">
-      <c r="A98" s="90"/>
+      <c r="A98" s="89"/>
     </row>
     <row r="99">
-      <c r="A99" s="90"/>
+      <c r="A99" s="89"/>
     </row>
     <row r="100">
-      <c r="A100" s="90"/>
+      <c r="A100" s="89"/>
     </row>
     <row r="101">
-      <c r="A101" s="90"/>
+      <c r="A101" s="89"/>
     </row>
     <row r="102">
-      <c r="A102" s="90"/>
+      <c r="A102" s="89"/>
     </row>
     <row r="103">
-      <c r="A103" s="90"/>
+      <c r="A103" s="89"/>
     </row>
     <row r="104">
-      <c r="A104" s="90"/>
+      <c r="A104" s="89"/>
     </row>
     <row r="105">
-      <c r="A105" s="90"/>
+      <c r="A105" s="89"/>
     </row>
     <row r="106">
-      <c r="A106" s="90"/>
+      <c r="A106" s="89"/>
     </row>
     <row r="107">
-      <c r="A107" s="90"/>
+      <c r="A107" s="89"/>
     </row>
     <row r="108">
-      <c r="A108" s="90"/>
+      <c r="A108" s="89"/>
     </row>
     <row r="109">
-      <c r="A109" s="90"/>
+      <c r="A109" s="89"/>
     </row>
     <row r="110">
-      <c r="A110" s="90"/>
+      <c r="A110" s="89"/>
     </row>
     <row r="111">
-      <c r="A111" s="90"/>
+      <c r="A111" s="89"/>
     </row>
     <row r="112">
-      <c r="A112" s="90"/>
+      <c r="A112" s="89"/>
     </row>
     <row r="113">
-      <c r="A113" s="90"/>
+      <c r="A113" s="89"/>
     </row>
     <row r="114">
-      <c r="A114" s="90"/>
+      <c r="A114" s="89"/>
     </row>
     <row r="115">
-      <c r="A115" s="90"/>
+      <c r="A115" s="89"/>
     </row>
     <row r="116">
-      <c r="A116" s="90"/>
+      <c r="A116" s="89"/>
     </row>
     <row r="117">
-      <c r="A117" s="90"/>
+      <c r="A117" s="89"/>
     </row>
     <row r="118">
-      <c r="A118" s="90"/>
+      <c r="A118" s="89"/>
     </row>
     <row r="119">
-      <c r="A119" s="90"/>
+      <c r="A119" s="89"/>
     </row>
     <row r="120">
-      <c r="A120" s="90"/>
+      <c r="A120" s="89"/>
     </row>
     <row r="121">
-      <c r="A121" s="90"/>
+      <c r="A121" s="89"/>
     </row>
     <row r="122">
-      <c r="A122" s="90"/>
+      <c r="A122" s="89"/>
     </row>
     <row r="123">
-      <c r="A123" s="90"/>
+      <c r="A123" s="89"/>
     </row>
     <row r="124">
-      <c r="A124" s="90"/>
+      <c r="A124" s="89"/>
     </row>
     <row r="125">
-      <c r="A125" s="90"/>
+      <c r="A125" s="89"/>
     </row>
     <row r="126">
-      <c r="A126" s="90"/>
+      <c r="A126" s="89"/>
     </row>
     <row r="127">
-      <c r="A127" s="90"/>
+      <c r="A127" s="89"/>
     </row>
     <row r="128">
-      <c r="A128" s="90"/>
+      <c r="A128" s="89"/>
     </row>
     <row r="129">
-      <c r="A129" s="90"/>
+      <c r="A129" s="89"/>
     </row>
     <row r="130">
-      <c r="A130" s="90"/>
+      <c r="A130" s="89"/>
     </row>
     <row r="131">
-      <c r="A131" s="90"/>
+      <c r="A131" s="89"/>
     </row>
     <row r="132">
-      <c r="A132" s="90"/>
+      <c r="A132" s="89"/>
     </row>
     <row r="133">
-      <c r="A133" s="90"/>
+      <c r="A133" s="89"/>
     </row>
     <row r="134">
-      <c r="A134" s="90"/>
+      <c r="A134" s="89"/>
     </row>
     <row r="135">
-      <c r="A135" s="90"/>
+      <c r="A135" s="89"/>
     </row>
     <row r="136">
-      <c r="A136" s="90"/>
+      <c r="A136" s="89"/>
     </row>
     <row r="137">
-      <c r="A137" s="90"/>
+      <c r="A137" s="89"/>
     </row>
     <row r="138">
-      <c r="A138" s="90"/>
+      <c r="A138" s="89"/>
     </row>
     <row r="139">
-      <c r="A139" s="90"/>
+      <c r="A139" s="89"/>
     </row>
     <row r="140">
-      <c r="A140" s="90"/>
+      <c r="A140" s="89"/>
     </row>
     <row r="141">
-      <c r="A141" s="90"/>
+      <c r="A141" s="89"/>
     </row>
     <row r="142">
-      <c r="A142" s="90"/>
+      <c r="A142" s="89"/>
     </row>
     <row r="143">
-      <c r="A143" s="90"/>
+      <c r="A143" s="89"/>
     </row>
     <row r="144">
-      <c r="A144" s="90"/>
+      <c r="A144" s="89"/>
     </row>
     <row r="145">
-      <c r="A145" s="90"/>
+      <c r="A145" s="89"/>
     </row>
     <row r="146">
-      <c r="A146" s="90"/>
+      <c r="A146" s="89"/>
     </row>
     <row r="147">
-      <c r="A147" s="90"/>
+      <c r="A147" s="89"/>
     </row>
     <row r="148">
-      <c r="A148" s="90"/>
+      <c r="A148" s="89"/>
     </row>
     <row r="149">
-      <c r="A149" s="90"/>
+      <c r="A149" s="89"/>
     </row>
     <row r="150">
-      <c r="A150" s="90"/>
+      <c r="A150" s="89"/>
     </row>
     <row r="151">
-      <c r="A151" s="90"/>
+      <c r="A151" s="89"/>
     </row>
     <row r="152">
-      <c r="A152" s="90"/>
+      <c r="A152" s="89"/>
     </row>
     <row r="153">
-      <c r="A153" s="90"/>
+      <c r="A153" s="89"/>
     </row>
     <row r="154">
-      <c r="A154" s="90"/>
+      <c r="A154" s="89"/>
     </row>
     <row r="155">
-      <c r="A155" s="90"/>
+      <c r="A155" s="89"/>
     </row>
     <row r="156">
-      <c r="A156" s="90"/>
+      <c r="A156" s="89"/>
     </row>
     <row r="157">
-      <c r="A157" s="90"/>
+      <c r="A157" s="89"/>
     </row>
     <row r="158">
-      <c r="A158" s="90"/>
+      <c r="A158" s="89"/>
     </row>
     <row r="159">
-      <c r="A159" s="90"/>
+      <c r="A159" s="89"/>
     </row>
     <row r="160">
-      <c r="A160" s="90"/>
+      <c r="A160" s="89"/>
     </row>
     <row r="161">
-      <c r="A161" s="90"/>
+      <c r="A161" s="89"/>
     </row>
     <row r="162">
-      <c r="A162" s="90"/>
+      <c r="A162" s="89"/>
     </row>
     <row r="163">
-      <c r="A163" s="90"/>
+      <c r="A163" s="89"/>
     </row>
     <row r="164">
-      <c r="A164" s="90"/>
+      <c r="A164" s="89"/>
     </row>
     <row r="165">
-      <c r="A165" s="90"/>
+      <c r="A165" s="89"/>
     </row>
     <row r="166">
-      <c r="A166" s="90"/>
+      <c r="A166" s="89"/>
     </row>
     <row r="167">
-      <c r="A167" s="90"/>
+      <c r="A167" s="89"/>
     </row>
     <row r="168">
-      <c r="A168" s="90"/>
+      <c r="A168" s="89"/>
     </row>
     <row r="169">
-      <c r="A169" s="90"/>
+      <c r="A169" s="89"/>
     </row>
     <row r="170">
-      <c r="A170" s="90"/>
+      <c r="A170" s="89"/>
     </row>
     <row r="171">
-      <c r="A171" s="90"/>
+      <c r="A171" s="89"/>
     </row>
     <row r="172">
-      <c r="A172" s="90"/>
+      <c r="A172" s="89"/>
     </row>
     <row r="173">
-      <c r="A173" s="90"/>
+      <c r="A173" s="89"/>
     </row>
     <row r="174">
-      <c r="A174" s="90"/>
+      <c r="A174" s="89"/>
     </row>
     <row r="175">
-      <c r="A175" s="90"/>
+      <c r="A175" s="89"/>
     </row>
     <row r="176">
-      <c r="A176" s="90"/>
+      <c r="A176" s="89"/>
     </row>
     <row r="177">
-      <c r="A177" s="90"/>
+      <c r="A177" s="89"/>
     </row>
     <row r="178">
-      <c r="A178" s="90"/>
+      <c r="A178" s="89"/>
     </row>
     <row r="179">
-      <c r="A179" s="90"/>
+      <c r="A179" s="89"/>
     </row>
     <row r="180">
-      <c r="A180" s="90"/>
+      <c r="A180" s="89"/>
     </row>
     <row r="181">
-      <c r="A181" s="90"/>
+      <c r="A181" s="89"/>
     </row>
     <row r="182">
-      <c r="A182" s="90"/>
+      <c r="A182" s="89"/>
     </row>
     <row r="183">
-      <c r="A183" s="90"/>
+      <c r="A183" s="89"/>
     </row>
     <row r="184">
-      <c r="A184" s="90"/>
+      <c r="A184" s="89"/>
     </row>
     <row r="185">
-      <c r="A185" s="90"/>
+      <c r="A185" s="89"/>
     </row>
     <row r="186">
-      <c r="A186" s="90"/>
+      <c r="A186" s="89"/>
     </row>
     <row r="187">
-      <c r="A187" s="90"/>
+      <c r="A187" s="89"/>
     </row>
     <row r="188">
-      <c r="A188" s="90"/>
+      <c r="A188" s="89"/>
     </row>
     <row r="189">
-      <c r="A189" s="90"/>
+      <c r="A189" s="89"/>
     </row>
     <row r="190">
-      <c r="A190" s="90"/>
+      <c r="A190" s="89"/>
     </row>
     <row r="191">
-      <c r="A191" s="90"/>
+      <c r="A191" s="89"/>
     </row>
     <row r="192">
-      <c r="A192" s="90"/>
+      <c r="A192" s="89"/>
     </row>
     <row r="193">
-      <c r="A193" s="90"/>
+      <c r="A193" s="89"/>
     </row>
     <row r="194">
-      <c r="A194" s="90"/>
+      <c r="A194" s="89"/>
     </row>
     <row r="195">
-      <c r="A195" s="90"/>
+      <c r="A195" s="89"/>
     </row>
     <row r="196">
-      <c r="A196" s="90"/>
+      <c r="A196" s="89"/>
     </row>
     <row r="197">
-      <c r="A197" s="90"/>
+      <c r="A197" s="89"/>
     </row>
     <row r="198">
-      <c r="A198" s="90"/>
+      <c r="A198" s="89"/>
     </row>
     <row r="199">
-      <c r="A199" s="90"/>
+      <c r="A199" s="89"/>
     </row>
     <row r="200">
-      <c r="A200" s="90"/>
+      <c r="A200" s="89"/>
     </row>
     <row r="201">
-      <c r="A201" s="90"/>
+      <c r="A201" s="89"/>
     </row>
     <row r="202">
-      <c r="A202" s="90"/>
+      <c r="A202" s="89"/>
     </row>
     <row r="203">
-      <c r="A203" s="90"/>
+      <c r="A203" s="89"/>
     </row>
     <row r="204">
-      <c r="A204" s="90"/>
+      <c r="A204" s="89"/>
     </row>
     <row r="205">
-      <c r="A205" s="90"/>
+      <c r="A205" s="89"/>
     </row>
     <row r="206">
-      <c r="A206" s="90"/>
+      <c r="A206" s="89"/>
     </row>
     <row r="207">
-      <c r="A207" s="90"/>
+      <c r="A207" s="89"/>
     </row>
     <row r="208">
-      <c r="A208" s="90"/>
+      <c r="A208" s="89"/>
     </row>
     <row r="209">
-      <c r="A209" s="90"/>
+      <c r="A209" s="89"/>
     </row>
     <row r="210">
-      <c r="A210" s="90"/>
+      <c r="A210" s="89"/>
     </row>
     <row r="211">
-      <c r="A211" s="90"/>
+      <c r="A211" s="89"/>
     </row>
     <row r="212">
-      <c r="A212" s="90"/>
+      <c r="A212" s="89"/>
     </row>
     <row r="213">
-      <c r="A213" s="90"/>
+      <c r="A213" s="89"/>
     </row>
     <row r="214">
-      <c r="A214" s="90"/>
+      <c r="A214" s="89"/>
     </row>
     <row r="215">
-      <c r="A215" s="90"/>
+      <c r="A215" s="89"/>
     </row>
     <row r="216">
-      <c r="A216" s="90"/>
+      <c r="A216" s="89"/>
     </row>
     <row r="217">
-      <c r="A217" s="90"/>
+      <c r="A217" s="89"/>
     </row>
     <row r="218">
-      <c r="A218" s="90"/>
+      <c r="A218" s="89"/>
     </row>
     <row r="219">
-      <c r="A219" s="90"/>
+      <c r="A219" s="89"/>
     </row>
     <row r="220">
-      <c r="A220" s="90"/>
+      <c r="A220" s="89"/>
     </row>
     <row r="221">
-      <c r="A221" s="90"/>
+      <c r="A221" s="89"/>
     </row>
     <row r="222">
-      <c r="A222" s="90"/>
+      <c r="A222" s="89"/>
     </row>
     <row r="223">
-      <c r="A223" s="90"/>
+      <c r="A223" s="89"/>
     </row>
     <row r="224">
-      <c r="A224" s="90"/>
+      <c r="A224" s="89"/>
     </row>
     <row r="225">
-      <c r="A225" s="90"/>
+      <c r="A225" s="89"/>
     </row>
     <row r="226">
-      <c r="A226" s="90"/>
+      <c r="A226" s="89"/>
     </row>
     <row r="227">
-      <c r="A227" s="90"/>
+      <c r="A227" s="89"/>
     </row>
     <row r="228">
-      <c r="A228" s="90"/>
+      <c r="A228" s="89"/>
     </row>
     <row r="229">
-      <c r="A229" s="90"/>
+      <c r="A229" s="89"/>
     </row>
     <row r="230">
-      <c r="A230" s="90"/>
+      <c r="A230" s="89"/>
     </row>
     <row r="231">
-      <c r="A231" s="90"/>
+      <c r="A231" s="89"/>
     </row>
     <row r="232">
-      <c r="A232" s="90"/>
+      <c r="A232" s="89"/>
     </row>
     <row r="233">
-      <c r="A233" s="90"/>
+      <c r="A233" s="89"/>
     </row>
     <row r="234">
-      <c r="A234" s="90"/>
+      <c r="A234" s="89"/>
     </row>
     <row r="235">
-      <c r="A235" s="90"/>
+      <c r="A235" s="89"/>
     </row>
     <row r="236">
-      <c r="A236" s="90"/>
+      <c r="A236" s="89"/>
     </row>
     <row r="237">
-      <c r="A237" s="90"/>
+      <c r="A237" s="89"/>
     </row>
     <row r="238">
-      <c r="A238" s="90"/>
+      <c r="A238" s="89"/>
     </row>
     <row r="239">
-      <c r="A239" s="90"/>
+      <c r="A239" s="89"/>
     </row>
     <row r="240">
-      <c r="A240" s="90"/>
+      <c r="A240" s="89"/>
     </row>
     <row r="241">
-      <c r="A241" s="90"/>
+      <c r="A241" s="89"/>
     </row>
     <row r="242">
-      <c r="A242" s="90"/>
+      <c r="A242" s="89"/>
     </row>
     <row r="243">
-      <c r="A243" s="90"/>
+      <c r="A243" s="89"/>
     </row>
     <row r="244">
-      <c r="A244" s="90"/>
+      <c r="A244" s="89"/>
     </row>
     <row r="245">
-      <c r="A245" s="90"/>
+      <c r="A245" s="89"/>
     </row>
     <row r="246">
-      <c r="A246" s="90"/>
+      <c r="A246" s="89"/>
     </row>
     <row r="247">
-      <c r="A247" s="90"/>
+      <c r="A247" s="89"/>
     </row>
     <row r="248">
-      <c r="A248" s="90"/>
+      <c r="A248" s="89"/>
     </row>
     <row r="249">
-      <c r="A249" s="90"/>
+      <c r="A249" s="89"/>
     </row>
     <row r="250">
-      <c r="A250" s="90"/>
+      <c r="A250" s="89"/>
     </row>
     <row r="251">
-      <c r="A251" s="90"/>
+      <c r="A251" s="89"/>
     </row>
     <row r="252">
-      <c r="A252" s="90"/>
+      <c r="A252" s="89"/>
     </row>
     <row r="253">
-      <c r="A253" s="90"/>
+      <c r="A253" s="89"/>
     </row>
     <row r="254">
-      <c r="A254" s="90"/>
+      <c r="A254" s="89"/>
     </row>
     <row r="255">
-      <c r="A255" s="90"/>
+      <c r="A255" s="89"/>
     </row>
     <row r="256">
-      <c r="A256" s="90"/>
+      <c r="A256" s="89"/>
     </row>
     <row r="257">
-      <c r="A257" s="90"/>
+      <c r="A257" s="89"/>
     </row>
     <row r="258">
-      <c r="A258" s="90"/>
+      <c r="A258" s="89"/>
     </row>
     <row r="259">
-      <c r="A259" s="90"/>
+      <c r="A259" s="89"/>
     </row>
     <row r="260">
-      <c r="A260" s="90"/>
+      <c r="A260" s="89"/>
     </row>
     <row r="261">
-      <c r="A261" s="90"/>
+      <c r="A261" s="89"/>
     </row>
     <row r="262">
-      <c r="A262" s="90"/>
+      <c r="A262" s="89"/>
     </row>
     <row r="263">
-      <c r="A263" s="90"/>
+      <c r="A263" s="89"/>
     </row>
     <row r="264">
-      <c r="A264" s="90"/>
+      <c r="A264" s="89"/>
     </row>
     <row r="265">
-      <c r="A265" s="90"/>
+      <c r="A265" s="89"/>
     </row>
     <row r="266">
-      <c r="A266" s="90"/>
+      <c r="A266" s="89"/>
     </row>
     <row r="267">
-      <c r="A267" s="90"/>
+      <c r="A267" s="89"/>
     </row>
     <row r="268">
-      <c r="A268" s="90"/>
+      <c r="A268" s="89"/>
     </row>
     <row r="269">
-      <c r="A269" s="90"/>
+      <c r="A269" s="89"/>
     </row>
     <row r="270">
-      <c r="A270" s="90"/>
+      <c r="A270" s="89"/>
     </row>
     <row r="271">
-      <c r="A271" s="90"/>
+      <c r="A271" s="89"/>
     </row>
     <row r="272">
-      <c r="A272" s="90"/>
+      <c r="A272" s="89"/>
     </row>
     <row r="273">
-      <c r="A273" s="90"/>
+      <c r="A273" s="89"/>
     </row>
     <row r="274">
-      <c r="A274" s="90"/>
+      <c r="A274" s="89"/>
     </row>
     <row r="275">
-      <c r="A275" s="90"/>
+      <c r="A275" s="89"/>
     </row>
     <row r="276">
-      <c r="A276" s="90"/>
+      <c r="A276" s="89"/>
     </row>
     <row r="277">
-      <c r="A277" s="90"/>
+      <c r="A277" s="89"/>
     </row>
     <row r="278">
-      <c r="A278" s="90"/>
+      <c r="A278" s="89"/>
     </row>
     <row r="279">
-      <c r="A279" s="90"/>
+      <c r="A279" s="89"/>
     </row>
     <row r="280">
-      <c r="A280" s="90"/>
+      <c r="A280" s="89"/>
     </row>
     <row r="281">
-      <c r="A281" s="90"/>
+      <c r="A281" s="89"/>
     </row>
     <row r="282">
-      <c r="A282" s="90"/>
+      <c r="A282" s="89"/>
     </row>
     <row r="283">
-      <c r="A283" s="90"/>
+      <c r="A283" s="89"/>
     </row>
     <row r="284">
-      <c r="A284" s="90"/>
+      <c r="A284" s="89"/>
     </row>
     <row r="285">
-      <c r="A285" s="90"/>
+      <c r="A285" s="89"/>
     </row>
     <row r="286">
-      <c r="A286" s="90"/>
+      <c r="A286" s="89"/>
     </row>
     <row r="287">
-      <c r="A287" s="90"/>
+      <c r="A287" s="89"/>
     </row>
     <row r="288">
-      <c r="A288" s="90"/>
+      <c r="A288" s="89"/>
     </row>
     <row r="289">
-      <c r="A289" s="90"/>
+      <c r="A289" s="89"/>
     </row>
     <row r="290">
-      <c r="A290" s="90"/>
+      <c r="A290" s="89"/>
     </row>
     <row r="291">
-      <c r="A291" s="90"/>
+      <c r="A291" s="89"/>
     </row>
     <row r="292">
-      <c r="A292" s="90"/>
+      <c r="A292" s="89"/>
     </row>
     <row r="293">
-      <c r="A293" s="90"/>
+      <c r="A293" s="89"/>
     </row>
     <row r="294">
-      <c r="A294" s="90"/>
+      <c r="A294" s="89"/>
     </row>
     <row r="295">
-      <c r="A295" s="90"/>
+      <c r="A295" s="89"/>
     </row>
     <row r="296">
-      <c r="A296" s="90"/>
+      <c r="A296" s="89"/>
     </row>
     <row r="297">
-      <c r="A297" s="90"/>
+      <c r="A297" s="89"/>
     </row>
     <row r="298">
-      <c r="A298" s="90"/>
+      <c r="A298" s="89"/>
     </row>
     <row r="299">
-      <c r="A299" s="90"/>
+      <c r="A299" s="89"/>
     </row>
     <row r="300">
-      <c r="A300" s="90"/>
+      <c r="A300" s="89"/>
     </row>
     <row r="301">
-      <c r="A301" s="90"/>
+      <c r="A301" s="89"/>
     </row>
     <row r="302">
-      <c r="A302" s="90"/>
+      <c r="A302" s="89"/>
     </row>
     <row r="303">
-      <c r="A303" s="90"/>
+      <c r="A303" s="89"/>
     </row>
     <row r="304">
-      <c r="A304" s="90"/>
+      <c r="A304" s="89"/>
     </row>
     <row r="305">
-      <c r="A305" s="90"/>
+      <c r="A305" s="89"/>
     </row>
     <row r="306">
-      <c r="A306" s="90"/>
+      <c r="A306" s="89"/>
     </row>
     <row r="307">
-      <c r="A307" s="90"/>
+      <c r="A307" s="89"/>
     </row>
     <row r="308">
-      <c r="A308" s="90"/>
+      <c r="A308" s="89"/>
     </row>
     <row r="309">
-      <c r="A309" s="90"/>
+      <c r="A309" s="89"/>
     </row>
     <row r="310">
-      <c r="A310" s="90"/>
+      <c r="A310" s="89"/>
     </row>
     <row r="311">
-      <c r="A311" s="90"/>
+      <c r="A311" s="89"/>
     </row>
     <row r="312">
-      <c r="A312" s="90"/>
+      <c r="A312" s="89"/>
     </row>
     <row r="313">
-      <c r="A313" s="90"/>
+      <c r="A313" s="89"/>
     </row>
     <row r="314">
-      <c r="A314" s="90"/>
+      <c r="A314" s="89"/>
     </row>
     <row r="315">
-      <c r="A315" s="90"/>
+      <c r="A315" s="89"/>
     </row>
     <row r="316">
-      <c r="A316" s="90"/>
+      <c r="A316" s="89"/>
     </row>
     <row r="317">
-      <c r="A317" s="90"/>
+      <c r="A317" s="89"/>
     </row>
     <row r="318">
-      <c r="A318" s="90"/>
+      <c r="A318" s="89"/>
     </row>
     <row r="319">
-      <c r="A319" s="90"/>
+      <c r="A319" s="89"/>
     </row>
     <row r="320">
-      <c r="A320" s="90"/>
+      <c r="A320" s="89"/>
     </row>
     <row r="321">
-      <c r="A321" s="90"/>
+      <c r="A321" s="89"/>
     </row>
     <row r="322">
-      <c r="A322" s="90"/>
+      <c r="A322" s="89"/>
     </row>
     <row r="323">
-      <c r="A323" s="90"/>
+      <c r="A323" s="89"/>
     </row>
     <row r="324">
-      <c r="A324" s="90"/>
+      <c r="A324" s="89"/>
     </row>
     <row r="325">
-      <c r="A325" s="90"/>
+      <c r="A325" s="89"/>
     </row>
     <row r="326">
-      <c r="A326" s="90"/>
+      <c r="A326" s="89"/>
     </row>
     <row r="327">
-      <c r="A327" s="90"/>
+      <c r="A327" s="89"/>
     </row>
     <row r="328">
-      <c r="A328" s="90"/>
+      <c r="A328" s="89"/>
     </row>
     <row r="329">
-      <c r="A329" s="90"/>
+      <c r="A329" s="89"/>
     </row>
     <row r="330">
-      <c r="A330" s="90"/>
+      <c r="A330" s="89"/>
     </row>
     <row r="331">
-      <c r="A331" s="90"/>
+      <c r="A331" s="89"/>
     </row>
     <row r="332">
-      <c r="A332" s="90"/>
+      <c r="A332" s="89"/>
     </row>
     <row r="333">
-      <c r="A333" s="90"/>
+      <c r="A333" s="89"/>
     </row>
     <row r="334">
-      <c r="A334" s="90"/>
+      <c r="A334" s="89"/>
     </row>
     <row r="335">
-      <c r="A335" s="90"/>
+      <c r="A335" s="89"/>
     </row>
     <row r="336">
-      <c r="A336" s="90"/>
+      <c r="A336" s="89"/>
     </row>
     <row r="337">
-      <c r="A337" s="90"/>
+      <c r="A337" s="89"/>
     </row>
     <row r="338">
-      <c r="A338" s="90"/>
+      <c r="A338" s="89"/>
     </row>
     <row r="339">
-      <c r="A339" s="90"/>
+      <c r="A339" s="89"/>
     </row>
     <row r="340">
-      <c r="A340" s="90"/>
+      <c r="A340" s="89"/>
     </row>
     <row r="341">
-      <c r="A341" s="90"/>
+      <c r="A341" s="89"/>
     </row>
     <row r="342">
-      <c r="A342" s="90"/>
+      <c r="A342" s="89"/>
     </row>
     <row r="343">
-      <c r="A343" s="90"/>
+      <c r="A343" s="89"/>
     </row>
     <row r="344">
-      <c r="A344" s="90"/>
+      <c r="A344" s="89"/>
     </row>
     <row r="345">
-      <c r="A345" s="90"/>
+      <c r="A345" s="89"/>
     </row>
     <row r="346">
-      <c r="A346" s="90"/>
+      <c r="A346" s="89"/>
     </row>
     <row r="347">
-      <c r="A347" s="90"/>
+      <c r="A347" s="89"/>
     </row>
     <row r="348">
-      <c r="A348" s="90"/>
+      <c r="A348" s="89"/>
     </row>
     <row r="349">
-      <c r="A349" s="90"/>
+      <c r="A349" s="89"/>
     </row>
     <row r="350">
-      <c r="A350" s="90"/>
+      <c r="A350" s="89"/>
     </row>
     <row r="351">
-      <c r="A351" s="90"/>
+      <c r="A351" s="89"/>
     </row>
     <row r="352">
-      <c r="A352" s="90"/>
+      <c r="A352" s="89"/>
     </row>
     <row r="353">
-      <c r="A353" s="90"/>
+      <c r="A353" s="89"/>
     </row>
     <row r="354">
-      <c r="A354" s="90"/>
+      <c r="A354" s="89"/>
     </row>
     <row r="355">
-      <c r="A355" s="90"/>
+      <c r="A355" s="89"/>
     </row>
     <row r="356">
-      <c r="A356" s="90"/>
+      <c r="A356" s="89"/>
     </row>
     <row r="357">
-      <c r="A357" s="90"/>
+      <c r="A357" s="89"/>
     </row>
     <row r="358">
-      <c r="A358" s="90"/>
+      <c r="A358" s="89"/>
     </row>
     <row r="359">
-      <c r="A359" s="90"/>
+      <c r="A359" s="89"/>
     </row>
     <row r="360">
-      <c r="A360" s="90"/>
+      <c r="A360" s="89"/>
     </row>
     <row r="361">
-      <c r="A361" s="90"/>
+      <c r="A361" s="89"/>
     </row>
     <row r="362">
-      <c r="A362" s="90"/>
+      <c r="A362" s="89"/>
     </row>
     <row r="363">
-      <c r="A363" s="90"/>
+      <c r="A363" s="89"/>
     </row>
     <row r="364">
-      <c r="A364" s="90"/>
+      <c r="A364" s="89"/>
     </row>
     <row r="365">
-      <c r="A365" s="90"/>
+      <c r="A365" s="89"/>
     </row>
     <row r="366">
-      <c r="A366" s="90"/>
+      <c r="A366" s="89"/>
     </row>
     <row r="367">
-      <c r="A367" s="90"/>
+      <c r="A367" s="89"/>
     </row>
     <row r="368">
-      <c r="A368" s="90"/>
+      <c r="A368" s="89"/>
     </row>
     <row r="369">
-      <c r="A369" s="90"/>
+      <c r="A369" s="89"/>
     </row>
     <row r="370">
-      <c r="A370" s="90"/>
+      <c r="A370" s="89"/>
     </row>
     <row r="371">
-      <c r="A371" s="90"/>
+      <c r="A371" s="89"/>
     </row>
     <row r="372">
-      <c r="A372" s="90"/>
+      <c r="A372" s="89"/>
     </row>
     <row r="373">
-      <c r="A373" s="90"/>
+      <c r="A373" s="89"/>
     </row>
     <row r="374">
-      <c r="A374" s="90"/>
+      <c r="A374" s="89"/>
     </row>
     <row r="375">
-      <c r="A375" s="90"/>
+      <c r="A375" s="89"/>
     </row>
     <row r="376">
-      <c r="A376" s="90"/>
+      <c r="A376" s="89"/>
     </row>
     <row r="377">
-      <c r="A377" s="90"/>
+      <c r="A377" s="89"/>
     </row>
     <row r="378">
-      <c r="A378" s="90"/>
+      <c r="A378" s="89"/>
     </row>
     <row r="379">
-      <c r="A379" s="90"/>
+      <c r="A379" s="89"/>
     </row>
     <row r="380">
-      <c r="A380" s="90"/>
+      <c r="A380" s="89"/>
     </row>
     <row r="381">
-      <c r="A381" s="90"/>
+      <c r="A381" s="89"/>
     </row>
     <row r="382">
-      <c r="A382" s="90"/>
+      <c r="A382" s="89"/>
     </row>
     <row r="383">
-      <c r="A383" s="90"/>
+      <c r="A383" s="89"/>
     </row>
     <row r="384">
-      <c r="A384" s="90"/>
+      <c r="A384" s="89"/>
     </row>
     <row r="385">
-      <c r="A385" s="90"/>
+      <c r="A385" s="89"/>
     </row>
     <row r="386">
-      <c r="A386" s="90"/>
+      <c r="A386" s="89"/>
     </row>
     <row r="387">
-      <c r="A387" s="90"/>
+      <c r="A387" s="89"/>
     </row>
     <row r="388">
-      <c r="A388" s="90"/>
+      <c r="A388" s="89"/>
     </row>
     <row r="389">
-      <c r="A389" s="90"/>
+      <c r="A389" s="89"/>
     </row>
     <row r="390">
-      <c r="A390" s="90"/>
+      <c r="A390" s="89"/>
     </row>
     <row r="391">
-      <c r="A391" s="90"/>
+      <c r="A391" s="89"/>
     </row>
     <row r="392">
-      <c r="A392" s="90"/>
+      <c r="A392" s="89"/>
     </row>
     <row r="393">
-      <c r="A393" s="90"/>
+      <c r="A393" s="89"/>
     </row>
     <row r="394">
-      <c r="A394" s="90"/>
+      <c r="A394" s="89"/>
     </row>
     <row r="395">
-      <c r="A395" s="90"/>
+      <c r="A395" s="89"/>
     </row>
     <row r="396">
-      <c r="A396" s="90"/>
+      <c r="A396" s="89"/>
     </row>
     <row r="397">
-      <c r="A397" s="90"/>
+      <c r="A397" s="89"/>
     </row>
     <row r="398">
-      <c r="A398" s="90"/>
+      <c r="A398" s="89"/>
     </row>
     <row r="399">
-      <c r="A399" s="90"/>
+      <c r="A399" s="89"/>
     </row>
     <row r="400">
-      <c r="A400" s="90"/>
+      <c r="A400" s="89"/>
     </row>
     <row r="401">
-      <c r="A401" s="90"/>
+      <c r="A401" s="89"/>
     </row>
     <row r="402">
-      <c r="A402" s="90"/>
+      <c r="A402" s="89"/>
     </row>
     <row r="403">
-      <c r="A403" s="90"/>
+      <c r="A403" s="89"/>
     </row>
     <row r="404">
-      <c r="A404" s="90"/>
+      <c r="A404" s="89"/>
     </row>
     <row r="405">
-      <c r="A405" s="90"/>
+      <c r="A405" s="89"/>
     </row>
     <row r="406">
-      <c r="A406" s="90"/>
+      <c r="A406" s="89"/>
     </row>
     <row r="407">
-      <c r="A407" s="90"/>
+      <c r="A407" s="89"/>
     </row>
     <row r="408">
-      <c r="A408" s="90"/>
+      <c r="A408" s="89"/>
     </row>
     <row r="409">
-      <c r="A409" s="90"/>
+      <c r="A409" s="89"/>
     </row>
     <row r="410">
-      <c r="A410" s="90"/>
+      <c r="A410" s="89"/>
     </row>
     <row r="411">
-      <c r="A411" s="90"/>
+      <c r="A411" s="89"/>
     </row>
     <row r="412">
-      <c r="A412" s="90"/>
+      <c r="A412" s="89"/>
     </row>
     <row r="413">
-      <c r="A413" s="90"/>
+      <c r="A413" s="89"/>
     </row>
     <row r="414">
-      <c r="A414" s="90"/>
+      <c r="A414" s="89"/>
     </row>
     <row r="415">
-      <c r="A415" s="90"/>
+      <c r="A415" s="89"/>
     </row>
     <row r="416">
-      <c r="A416" s="90"/>
+      <c r="A416" s="89"/>
     </row>
     <row r="417">
-      <c r="A417" s="90"/>
+      <c r="A417" s="89"/>
     </row>
     <row r="418">
-      <c r="A418" s="90"/>
+      <c r="A418" s="89"/>
     </row>
     <row r="419">
-      <c r="A419" s="90"/>
+      <c r="A419" s="89"/>
     </row>
     <row r="420">
-      <c r="A420" s="90"/>
+      <c r="A420" s="89"/>
     </row>
     <row r="421">
-      <c r="A421" s="90"/>
+      <c r="A421" s="89"/>
     </row>
     <row r="422">
-      <c r="A422" s="90"/>
+      <c r="A422" s="89"/>
     </row>
     <row r="423">
-      <c r="A423" s="90"/>
+      <c r="A423" s="89"/>
     </row>
     <row r="424">
-      <c r="A424" s="90"/>
+      <c r="A424" s="89"/>
     </row>
     <row r="425">
-      <c r="A425" s="90"/>
+      <c r="A425" s="89"/>
     </row>
     <row r="426">
-      <c r="A426" s="90"/>
+      <c r="A426" s="89"/>
     </row>
     <row r="427">
-      <c r="A427" s="90"/>
+      <c r="A427" s="89"/>
     </row>
     <row r="428">
-      <c r="A428" s="90"/>
+      <c r="A428" s="89"/>
     </row>
     <row r="429">
-      <c r="A429" s="90"/>
+      <c r="A429" s="89"/>
     </row>
     <row r="430">
-      <c r="A430" s="90"/>
+      <c r="A430" s="89"/>
     </row>
     <row r="431">
-      <c r="A431" s="90"/>
+      <c r="A431" s="89"/>
     </row>
     <row r="432">
-      <c r="A432" s="90"/>
+      <c r="A432" s="89"/>
     </row>
     <row r="433">
-      <c r="A433" s="90"/>
+      <c r="A433" s="89"/>
     </row>
     <row r="434">
-      <c r="A434" s="90"/>
+      <c r="A434" s="89"/>
     </row>
     <row r="435">
-      <c r="A435" s="90"/>
+      <c r="A435" s="89"/>
     </row>
     <row r="436">
-      <c r="A436" s="90"/>
+      <c r="A436" s="89"/>
     </row>
     <row r="437">
-      <c r="A437" s="90"/>
+      <c r="A437" s="89"/>
     </row>
     <row r="438">
-      <c r="A438" s="90"/>
+      <c r="A438" s="89"/>
     </row>
     <row r="439">
-      <c r="A439" s="90"/>
+      <c r="A439" s="89"/>
     </row>
     <row r="440">
-      <c r="A440" s="90"/>
+      <c r="A440" s="89"/>
     </row>
     <row r="441">
-      <c r="A441" s="90"/>
+      <c r="A441" s="89"/>
     </row>
     <row r="442">
-      <c r="A442" s="90"/>
+      <c r="A442" s="89"/>
     </row>
     <row r="443">
-      <c r="A443" s="90"/>
+      <c r="A443" s="89"/>
     </row>
     <row r="444">
-      <c r="A444" s="90"/>
+      <c r="A444" s="89"/>
     </row>
     <row r="445">
-      <c r="A445" s="90"/>
+      <c r="A445" s="89"/>
     </row>
     <row r="446">
-      <c r="A446" s="90"/>
+      <c r="A446" s="89"/>
     </row>
     <row r="447">
-      <c r="A447" s="90"/>
+      <c r="A447" s="89"/>
     </row>
     <row r="448">
-      <c r="A448" s="90"/>
+      <c r="A448" s="89"/>
     </row>
     <row r="449">
-      <c r="A449" s="90"/>
+      <c r="A449" s="89"/>
     </row>
     <row r="450">
-      <c r="A450" s="90"/>
+      <c r="A450" s="89"/>
     </row>
     <row r="451">
-      <c r="A451" s="90"/>
+      <c r="A451" s="89"/>
     </row>
     <row r="452">
-      <c r="A452" s="90"/>
+      <c r="A452" s="89"/>
     </row>
     <row r="453">
-      <c r="A453" s="90"/>
+      <c r="A453" s="89"/>
     </row>
     <row r="454">
-      <c r="A454" s="90"/>
+      <c r="A454" s="89"/>
     </row>
     <row r="455">
-      <c r="A455" s="90"/>
+      <c r="A455" s="89"/>
     </row>
     <row r="456">
-      <c r="A456" s="90"/>
+      <c r="A456" s="89"/>
     </row>
     <row r="457">
-      <c r="A457" s="90"/>
+      <c r="A457" s="89"/>
     </row>
     <row r="458">
-      <c r="A458" s="90"/>
+      <c r="A458" s="89"/>
     </row>
     <row r="459">
-      <c r="A459" s="90"/>
+      <c r="A459" s="89"/>
     </row>
     <row r="460">
-      <c r="A460" s="90"/>
+      <c r="A460" s="89"/>
     </row>
     <row r="461">
-      <c r="A461" s="90"/>
+      <c r="A461" s="89"/>
     </row>
     <row r="462">
-      <c r="A462" s="90"/>
+      <c r="A462" s="89"/>
     </row>
     <row r="463">
-      <c r="A463" s="90"/>
+      <c r="A463" s="89"/>
     </row>
     <row r="464">
-      <c r="A464" s="90"/>
+      <c r="A464" s="89"/>
     </row>
     <row r="465">
-      <c r="A465" s="90"/>
+      <c r="A465" s="89"/>
     </row>
     <row r="466">
-      <c r="A466" s="90"/>
+      <c r="A466" s="89"/>
     </row>
     <row r="467">
-      <c r="A467" s="90"/>
+      <c r="A467" s="89"/>
     </row>
     <row r="468">
-      <c r="A468" s="90"/>
+      <c r="A468" s="89"/>
     </row>
     <row r="469">
-      <c r="A469" s="90"/>
+      <c r="A469" s="89"/>
     </row>
     <row r="470">
-      <c r="A470" s="90"/>
+      <c r="A470" s="89"/>
     </row>
     <row r="471">
-      <c r="A471" s="90"/>
+      <c r="A471" s="89"/>
     </row>
     <row r="472">
-      <c r="A472" s="90"/>
+      <c r="A472" s="89"/>
     </row>
     <row r="473">
-      <c r="A473" s="90"/>
+      <c r="A473" s="89"/>
     </row>
     <row r="474">
-      <c r="A474" s="90"/>
+      <c r="A474" s="89"/>
     </row>
     <row r="475">
-      <c r="A475" s="90"/>
+      <c r="A475" s="89"/>
     </row>
     <row r="476">
-      <c r="A476" s="90"/>
+      <c r="A476" s="89"/>
     </row>
     <row r="477">
-      <c r="A477" s="90"/>
+      <c r="A477" s="89"/>
     </row>
     <row r="478">
-      <c r="A478" s="90"/>
+      <c r="A478" s="89"/>
     </row>
     <row r="479">
-      <c r="A479" s="90"/>
+      <c r="A479" s="89"/>
     </row>
     <row r="480">
-      <c r="A480" s="90"/>
+      <c r="A480" s="89"/>
     </row>
     <row r="481">
-      <c r="A481" s="90"/>
+      <c r="A481" s="89"/>
     </row>
     <row r="482">
-      <c r="A482" s="90"/>
+      <c r="A482" s="89"/>
     </row>
     <row r="483">
-      <c r="A483" s="90"/>
+      <c r="A483" s="89"/>
     </row>
     <row r="484">
-      <c r="A484" s="90"/>
+      <c r="A484" s="89"/>
     </row>
     <row r="485">
-      <c r="A485" s="90"/>
+      <c r="A485" s="89"/>
     </row>
     <row r="486">
-      <c r="A486" s="90"/>
+      <c r="A486" s="89"/>
     </row>
     <row r="487">
-      <c r="A487" s="90"/>
+      <c r="A487" s="89"/>
     </row>
     <row r="488">
-      <c r="A488" s="90"/>
+      <c r="A488" s="89"/>
     </row>
     <row r="489">
-      <c r="A489" s="90"/>
+      <c r="A489" s="89"/>
     </row>
     <row r="490">
-      <c r="A490" s="90"/>
+      <c r="A490" s="89"/>
     </row>
     <row r="491">
-      <c r="A491" s="90"/>
+      <c r="A491" s="89"/>
     </row>
     <row r="492">
-      <c r="A492" s="90"/>
+      <c r="A492" s="89"/>
     </row>
     <row r="493">
-      <c r="A493" s="90"/>
+      <c r="A493" s="89"/>
     </row>
     <row r="494">
-      <c r="A494" s="90"/>
+      <c r="A494" s="89"/>
     </row>
     <row r="495">
-      <c r="A495" s="90"/>
+      <c r="A495" s="89"/>
     </row>
     <row r="496">
-      <c r="A496" s="90"/>
+      <c r="A496" s="89"/>
     </row>
     <row r="497">
-      <c r="A497" s="90"/>
+      <c r="A497" s="89"/>
     </row>
     <row r="498">
-      <c r="A498" s="90"/>
+      <c r="A498" s="89"/>
     </row>
     <row r="499">
-      <c r="A499" s="90"/>
+      <c r="A499" s="89"/>
     </row>
     <row r="500">
-      <c r="A500" s="90"/>
+      <c r="A500" s="89"/>
     </row>
     <row r="501">
-      <c r="A501" s="90"/>
+      <c r="A501" s="89"/>
     </row>
     <row r="502">
-      <c r="A502" s="90"/>
+      <c r="A502" s="89"/>
     </row>
     <row r="503">
-      <c r="A503" s="90"/>
+      <c r="A503" s="89"/>
     </row>
     <row r="504">
-      <c r="A504" s="90"/>
+      <c r="A504" s="89"/>
     </row>
     <row r="505">
-      <c r="A505" s="90"/>
+      <c r="A505" s="89"/>
     </row>
     <row r="506">
-      <c r="A506" s="90"/>
+      <c r="A506" s="89"/>
     </row>
     <row r="507">
-      <c r="A507" s="90"/>
+      <c r="A507" s="89"/>
     </row>
     <row r="508">
-      <c r="A508" s="90"/>
+      <c r="A508" s="89"/>
     </row>
     <row r="509">
-      <c r="A509" s="90"/>
+      <c r="A509" s="89"/>
     </row>
     <row r="510">
-      <c r="A510" s="90"/>
+      <c r="A510" s="89"/>
     </row>
     <row r="511">
-      <c r="A511" s="90"/>
+      <c r="A511" s="89"/>
     </row>
     <row r="512">
-      <c r="A512" s="90"/>
+      <c r="A512" s="89"/>
     </row>
     <row r="513">
-      <c r="A513" s="90"/>
+      <c r="A513" s="89"/>
     </row>
     <row r="514">
-      <c r="A514" s="90"/>
+      <c r="A514" s="89"/>
     </row>
     <row r="515">
-      <c r="A515" s="90"/>
+      <c r="A515" s="89"/>
     </row>
     <row r="516">
-      <c r="A516" s="90"/>
+      <c r="A516" s="89"/>
     </row>
     <row r="517">
-      <c r="A517" s="90"/>
+      <c r="A517" s="89"/>
     </row>
     <row r="518">
-      <c r="A518" s="90"/>
+      <c r="A518" s="89"/>
     </row>
     <row r="519">
-      <c r="A519" s="90"/>
+      <c r="A519" s="89"/>
     </row>
     <row r="520">
-      <c r="A520" s="90"/>
+      <c r="A520" s="89"/>
     </row>
     <row r="521">
-      <c r="A521" s="90"/>
+      <c r="A521" s="89"/>
     </row>
     <row r="522">
-      <c r="A522" s="90"/>
+      <c r="A522" s="89"/>
     </row>
     <row r="523">
-      <c r="A523" s="90"/>
+      <c r="A523" s="89"/>
     </row>
     <row r="524">
-      <c r="A524" s="90"/>
+      <c r="A524" s="89"/>
     </row>
     <row r="525">
-      <c r="A525" s="90"/>
+      <c r="A525" s="89"/>
     </row>
     <row r="526">
-      <c r="A526" s="90"/>
+      <c r="A526" s="89"/>
     </row>
     <row r="527">
-      <c r="A527" s="90"/>
+      <c r="A527" s="89"/>
     </row>
     <row r="528">
-      <c r="A528" s="90"/>
+      <c r="A528" s="89"/>
     </row>
     <row r="529">
-      <c r="A529" s="90"/>
+      <c r="A529" s="89"/>
     </row>
     <row r="530">
-      <c r="A530" s="90"/>
+      <c r="A530" s="89"/>
     </row>
     <row r="531">
-      <c r="A531" s="90"/>
+      <c r="A531" s="89"/>
     </row>
     <row r="532">
-      <c r="A532" s="90"/>
+      <c r="A532" s="89"/>
     </row>
     <row r="533">
-      <c r="A533" s="90"/>
+      <c r="A533" s="89"/>
     </row>
     <row r="534">
-      <c r="A534" s="90"/>
+      <c r="A534" s="89"/>
     </row>
     <row r="535">
-      <c r="A535" s="90"/>
+      <c r="A535" s="89"/>
     </row>
     <row r="536">
-      <c r="A536" s="90"/>
+      <c r="A536" s="89"/>
     </row>
     <row r="537">
-      <c r="A537" s="90"/>
+      <c r="A537" s="89"/>
     </row>
     <row r="538">
-      <c r="A538" s="90"/>
+      <c r="A538" s="89"/>
     </row>
     <row r="539">
-      <c r="A539" s="90"/>
+      <c r="A539" s="89"/>
     </row>
     <row r="540">
-      <c r="A540" s="90"/>
+      <c r="A540" s="89"/>
     </row>
     <row r="541">
-      <c r="A541" s="90"/>
+      <c r="A541" s="89"/>
     </row>
     <row r="542">
-      <c r="A542" s="90"/>
+      <c r="A542" s="89"/>
     </row>
     <row r="543">
-      <c r="A543" s="90"/>
+      <c r="A543" s="89"/>
     </row>
     <row r="544">
-      <c r="A544" s="90"/>
+      <c r="A544" s="89"/>
     </row>
     <row r="545">
-      <c r="A545" s="90"/>
+      <c r="A545" s="89"/>
     </row>
     <row r="546">
-      <c r="A546" s="90"/>
+      <c r="A546" s="89"/>
     </row>
     <row r="547">
-      <c r="A547" s="90"/>
+      <c r="A547" s="89"/>
     </row>
     <row r="548">
-      <c r="A548" s="90"/>
+      <c r="A548" s="89"/>
     </row>
     <row r="549">
-      <c r="A549" s="90"/>
+      <c r="A549" s="89"/>
     </row>
     <row r="550">
-      <c r="A550" s="90"/>
+      <c r="A550" s="89"/>
     </row>
     <row r="551">
-      <c r="A551" s="90"/>
+      <c r="A551" s="89"/>
     </row>
     <row r="552">
-      <c r="A552" s="90"/>
+      <c r="A552" s="89"/>
     </row>
     <row r="553">
-      <c r="A553" s="90"/>
+      <c r="A553" s="89"/>
     </row>
     <row r="554">
-      <c r="A554" s="90"/>
+      <c r="A554" s="89"/>
     </row>
     <row r="555">
-      <c r="A555" s="90"/>
+      <c r="A555" s="89"/>
     </row>
     <row r="556">
-      <c r="A556" s="90"/>
+      <c r="A556" s="89"/>
     </row>
     <row r="557">
-      <c r="A557" s="90"/>
+      <c r="A557" s="89"/>
     </row>
     <row r="558">
-      <c r="A558" s="90"/>
+      <c r="A558" s="89"/>
     </row>
     <row r="559">
-      <c r="A559" s="90"/>
+      <c r="A559" s="89"/>
     </row>
     <row r="560">
-      <c r="A560" s="90"/>
+      <c r="A560" s="89"/>
     </row>
     <row r="561">
-      <c r="A561" s="90"/>
+      <c r="A561" s="89"/>
     </row>
     <row r="562">
-      <c r="A562" s="90"/>
+      <c r="A562" s="89"/>
     </row>
     <row r="563">
-      <c r="A563" s="90"/>
+      <c r="A563" s="89"/>
     </row>
     <row r="564">
-      <c r="A564" s="90"/>
+      <c r="A564" s="89"/>
     </row>
     <row r="565">
-      <c r="A565" s="90"/>
+      <c r="A565" s="89"/>
     </row>
     <row r="566">
-      <c r="A566" s="90"/>
+      <c r="A566" s="89"/>
     </row>
     <row r="567">
-      <c r="A567" s="90"/>
+      <c r="A567" s="89"/>
     </row>
     <row r="568">
-      <c r="A568" s="90"/>
+      <c r="A568" s="89"/>
     </row>
     <row r="569">
-      <c r="A569" s="90"/>
+      <c r="A569" s="89"/>
     </row>
     <row r="570">
-      <c r="A570" s="90"/>
+      <c r="A570" s="89"/>
     </row>
     <row r="571">
-      <c r="A571" s="90"/>
+      <c r="A571" s="89"/>
     </row>
     <row r="572">
-      <c r="A572" s="90"/>
+      <c r="A572" s="89"/>
     </row>
     <row r="573">
-      <c r="A573" s="90"/>
+      <c r="A573" s="89"/>
     </row>
     <row r="574">
-      <c r="A574" s="90"/>
+      <c r="A574" s="89"/>
     </row>
     <row r="575">
-      <c r="A575" s="90"/>
+      <c r="A575" s="89"/>
     </row>
     <row r="576">
-      <c r="A576" s="90"/>
+      <c r="A576" s="89"/>
     </row>
     <row r="577">
-      <c r="A577" s="90"/>
+      <c r="A577" s="89"/>
     </row>
     <row r="578">
-      <c r="A578" s="90"/>
+      <c r="A578" s="89"/>
     </row>
     <row r="579">
-      <c r="A579" s="90"/>
+      <c r="A579" s="89"/>
     </row>
     <row r="580">
-      <c r="A580" s="90"/>
+      <c r="A580" s="89"/>
     </row>
     <row r="581">
-      <c r="A581" s="90"/>
+      <c r="A581" s="89"/>
     </row>
     <row r="582">
-      <c r="A582" s="90"/>
+      <c r="A582" s="89"/>
     </row>
     <row r="583">
-      <c r="A583" s="90"/>
+      <c r="A583" s="89"/>
     </row>
     <row r="584">
-      <c r="A584" s="90"/>
+      <c r="A584" s="89"/>
     </row>
     <row r="585">
-      <c r="A585" s="90"/>
+      <c r="A585" s="89"/>
     </row>
     <row r="586">
-      <c r="A586" s="90"/>
+      <c r="A586" s="89"/>
     </row>
     <row r="587">
-      <c r="A587" s="90"/>
+      <c r="A587" s="89"/>
     </row>
     <row r="588">
-      <c r="A588" s="90"/>
+      <c r="A588" s="89"/>
     </row>
     <row r="589">
-      <c r="A589" s="90"/>
+      <c r="A589" s="89"/>
     </row>
     <row r="590">
-      <c r="A590" s="90"/>
+      <c r="A590" s="89"/>
     </row>
     <row r="591">
-      <c r="A591" s="90"/>
+      <c r="A591" s="89"/>
     </row>
     <row r="592">
-      <c r="A592" s="90"/>
+      <c r="A592" s="89"/>
     </row>
     <row r="593">
-      <c r="A593" s="90"/>
+      <c r="A593" s="89"/>
     </row>
     <row r="594">
-      <c r="A594" s="90"/>
+      <c r="A594" s="89"/>
     </row>
     <row r="595">
-      <c r="A595" s="90"/>
+      <c r="A595" s="89"/>
     </row>
     <row r="596">
-      <c r="A596" s="90"/>
+      <c r="A596" s="89"/>
     </row>
     <row r="597">
-      <c r="A597" s="90"/>
+      <c r="A597" s="89"/>
     </row>
     <row r="598">
-      <c r="A598" s="90"/>
+      <c r="A598" s="89"/>
     </row>
     <row r="599">
-      <c r="A599" s="90"/>
+      <c r="A599" s="89"/>
     </row>
     <row r="600">
-      <c r="A600" s="90"/>
+      <c r="A600" s="89"/>
     </row>
     <row r="601">
-      <c r="A601" s="90"/>
+      <c r="A601" s="89"/>
     </row>
     <row r="602">
-      <c r="A602" s="90"/>
+      <c r="A602" s="89"/>
     </row>
     <row r="603">
-      <c r="A603" s="90"/>
+      <c r="A603" s="89"/>
     </row>
     <row r="604">
-      <c r="A604" s="90"/>
+      <c r="A604" s="89"/>
     </row>
     <row r="605">
-      <c r="A605" s="90"/>
+      <c r="A605" s="89"/>
     </row>
     <row r="606">
-      <c r="A606" s="90"/>
+      <c r="A606" s="89"/>
     </row>
     <row r="607">
-      <c r="A607" s="90"/>
+      <c r="A607" s="89"/>
     </row>
     <row r="608">
-      <c r="A608" s="90"/>
+      <c r="A608" s="89"/>
     </row>
     <row r="609">
-      <c r="A609" s="90"/>
+      <c r="A609" s="89"/>
     </row>
     <row r="610">
-      <c r="A610" s="90"/>
+      <c r="A610" s="89"/>
     </row>
     <row r="611">
-      <c r="A611" s="90"/>
+      <c r="A611" s="89"/>
     </row>
     <row r="612">
-      <c r="A612" s="90"/>
+      <c r="A612" s="89"/>
     </row>
     <row r="613">
-      <c r="A613" s="90"/>
+      <c r="A613" s="89"/>
     </row>
     <row r="614">
-      <c r="A614" s="90"/>
+      <c r="A614" s="89"/>
     </row>
     <row r="615">
-      <c r="A615" s="90"/>
+      <c r="A615" s="89"/>
     </row>
     <row r="616">
-      <c r="A616" s="90"/>
+      <c r="A616" s="89"/>
     </row>
     <row r="617">
-      <c r="A617" s="90"/>
+      <c r="A617" s="89"/>
     </row>
     <row r="618">
-      <c r="A618" s="90"/>
+      <c r="A618" s="89"/>
     </row>
     <row r="619">
-      <c r="A619" s="90"/>
+      <c r="A619" s="89"/>
     </row>
     <row r="620">
-      <c r="A620" s="90"/>
+      <c r="A620" s="89"/>
     </row>
     <row r="621">
-      <c r="A621" s="90"/>
+      <c r="A621" s="89"/>
     </row>
     <row r="622">
-      <c r="A622" s="90"/>
+      <c r="A622" s="89"/>
     </row>
     <row r="623">
-      <c r="A623" s="90"/>
+      <c r="A623" s="89"/>
     </row>
     <row r="624">
-      <c r="A624" s="90"/>
+      <c r="A624" s="89"/>
     </row>
     <row r="625">
-      <c r="A625" s="90"/>
+      <c r="A625" s="89"/>
     </row>
     <row r="626">
-      <c r="A626" s="90"/>
+      <c r="A626" s="89"/>
     </row>
     <row r="627">
-      <c r="A627" s="90"/>
+      <c r="A627" s="89"/>
     </row>
     <row r="628">
-      <c r="A628" s="90"/>
+      <c r="A628" s="89"/>
     </row>
     <row r="629">
-      <c r="A629" s="90"/>
+      <c r="A629" s="89"/>
     </row>
     <row r="630">
-      <c r="A630" s="90"/>
+      <c r="A630" s="89"/>
     </row>
     <row r="631">
-      <c r="A631" s="90"/>
+      <c r="A631" s="89"/>
     </row>
     <row r="632">
-      <c r="A632" s="90"/>
+      <c r="A632" s="89"/>
     </row>
     <row r="633">
-      <c r="A633" s="90"/>
+      <c r="A633" s="89"/>
     </row>
     <row r="634">
-      <c r="A634" s="90"/>
+      <c r="A634" s="89"/>
     </row>
     <row r="635">
-      <c r="A635" s="90"/>
+      <c r="A635" s="89"/>
     </row>
     <row r="636">
-      <c r="A636" s="90"/>
+      <c r="A636" s="89"/>
     </row>
     <row r="637">
-      <c r="A637" s="90"/>
+      <c r="A637" s="89"/>
     </row>
     <row r="638">
-      <c r="A638" s="90"/>
+      <c r="A638" s="89"/>
     </row>
     <row r="639">
-      <c r="A639" s="90"/>
+      <c r="A639" s="89"/>
     </row>
     <row r="640">
-      <c r="A640" s="90"/>
+      <c r="A640" s="89"/>
     </row>
     <row r="641">
-      <c r="A641" s="90"/>
+      <c r="A641" s="89"/>
     </row>
     <row r="642">
-      <c r="A642" s="90"/>
+      <c r="A642" s="89"/>
     </row>
     <row r="643">
-      <c r="A643" s="90"/>
+      <c r="A643" s="89"/>
     </row>
     <row r="644">
-      <c r="A644" s="90"/>
+      <c r="A644" s="89"/>
     </row>
     <row r="645">
-      <c r="A645" s="90"/>
+      <c r="A645" s="89"/>
     </row>
     <row r="646">
-      <c r="A646" s="90"/>
+      <c r="A646" s="89"/>
     </row>
     <row r="647">
-      <c r="A647" s="90"/>
+      <c r="A647" s="89"/>
     </row>
     <row r="648">
-      <c r="A648" s="90"/>
+      <c r="A648" s="89"/>
     </row>
     <row r="649">
-      <c r="A649" s="90"/>
+      <c r="A649" s="89"/>
     </row>
     <row r="650">
-      <c r="A650" s="90"/>
+      <c r="A650" s="89"/>
     </row>
     <row r="651">
-      <c r="A651" s="90"/>
+      <c r="A651" s="89"/>
     </row>
     <row r="652">
-      <c r="A652" s="90"/>
+      <c r="A652" s="89"/>
     </row>
     <row r="653">
-      <c r="A653" s="90"/>
+      <c r="A653" s="89"/>
     </row>
     <row r="654">
-      <c r="A654" s="90"/>
+      <c r="A654" s="89"/>
     </row>
     <row r="655">
-      <c r="A655" s="90"/>
+      <c r="A655" s="89"/>
     </row>
     <row r="656">
-      <c r="A656" s="90"/>
+      <c r="A656" s="89"/>
     </row>
     <row r="657">
-      <c r="A657" s="90"/>
+      <c r="A657" s="89"/>
     </row>
     <row r="658">
-      <c r="A658" s="90"/>
+      <c r="A658" s="89"/>
     </row>
     <row r="659">
-      <c r="A659" s="90"/>
+      <c r="A659" s="89"/>
     </row>
     <row r="660">
-      <c r="A660" s="90"/>
+      <c r="A660" s="89"/>
     </row>
     <row r="661">
-      <c r="A661" s="90"/>
+      <c r="A661" s="89"/>
     </row>
     <row r="662">
-      <c r="A662" s="90"/>
+      <c r="A662" s="89"/>
     </row>
     <row r="663">
-      <c r="A663" s="90"/>
+      <c r="A663" s="89"/>
     </row>
     <row r="664">
-      <c r="A664" s="90"/>
+      <c r="A664" s="89"/>
     </row>
     <row r="665">
-      <c r="A665" s="90"/>
+      <c r="A665" s="89"/>
     </row>
     <row r="666">
-      <c r="A666" s="90"/>
+      <c r="A666" s="89"/>
     </row>
     <row r="667">
-      <c r="A667" s="90"/>
+      <c r="A667" s="89"/>
     </row>
     <row r="668">
-      <c r="A668" s="90"/>
+      <c r="A668" s="89"/>
     </row>
     <row r="669">
-      <c r="A669" s="90"/>
+      <c r="A669" s="89"/>
     </row>
     <row r="670">
-      <c r="A670" s="90"/>
+      <c r="A670" s="89"/>
     </row>
     <row r="671">
-      <c r="A671" s="90"/>
+      <c r="A671" s="89"/>
     </row>
     <row r="672">
-      <c r="A672" s="90"/>
+      <c r="A672" s="89"/>
     </row>
     <row r="673">
-      <c r="A673" s="90"/>
+      <c r="A673" s="89"/>
     </row>
     <row r="674">
-      <c r="A674" s="90"/>
+      <c r="A674" s="89"/>
     </row>
     <row r="675">
-      <c r="A675" s="90"/>
+      <c r="A675" s="89"/>
     </row>
     <row r="676">
-      <c r="A676" s="90"/>
+      <c r="A676" s="89"/>
     </row>
     <row r="677">
-      <c r="A677" s="90"/>
+      <c r="A677" s="89"/>
     </row>
     <row r="678">
-      <c r="A678" s="90"/>
+      <c r="A678" s="89"/>
     </row>
     <row r="679">
-      <c r="A679" s="90"/>
+      <c r="A679" s="89"/>
     </row>
     <row r="680">
-      <c r="A680" s="90"/>
+      <c r="A680" s="89"/>
     </row>
     <row r="681">
-      <c r="A681" s="90"/>
+      <c r="A681" s="89"/>
     </row>
     <row r="682">
-      <c r="A682" s="90"/>
+      <c r="A682" s="89"/>
     </row>
     <row r="683">
-      <c r="A683" s="90"/>
+      <c r="A683" s="89"/>
     </row>
     <row r="684">
-      <c r="A684" s="90"/>
+      <c r="A684" s="89"/>
     </row>
     <row r="685">
-      <c r="A685" s="90"/>
+      <c r="A685" s="89"/>
     </row>
     <row r="686">
-      <c r="A686" s="90"/>
+      <c r="A686" s="89"/>
     </row>
     <row r="687">
-      <c r="A687" s="90"/>
+      <c r="A687" s="89"/>
     </row>
     <row r="688">
-      <c r="A688" s="90"/>
+      <c r="A688" s="89"/>
     </row>
     <row r="689">
-      <c r="A689" s="90"/>
+      <c r="A689" s="89"/>
     </row>
     <row r="690">
-      <c r="A690" s="90"/>
+      <c r="A690" s="89"/>
     </row>
     <row r="691">
-      <c r="A691" s="90"/>
+      <c r="A691" s="89"/>
     </row>
     <row r="692">
-      <c r="A692" s="90"/>
+      <c r="A692" s="89"/>
     </row>
     <row r="693">
-      <c r="A693" s="90"/>
+      <c r="A693" s="89"/>
     </row>
     <row r="694">
-      <c r="A694" s="90"/>
+      <c r="A694" s="89"/>
     </row>
     <row r="695">
-      <c r="A695" s="90"/>
+      <c r="A695" s="89"/>
     </row>
     <row r="696">
-      <c r="A696" s="90"/>
+      <c r="A696" s="89"/>
     </row>
     <row r="697">
-      <c r="A697" s="90"/>
+      <c r="A697" s="89"/>
     </row>
     <row r="698">
-      <c r="A698" s="90"/>
+      <c r="A698" s="89"/>
     </row>
     <row r="699">
-      <c r="A699" s="90"/>
+      <c r="A699" s="89"/>
     </row>
     <row r="700">
-      <c r="A700" s="90"/>
+      <c r="A700" s="89"/>
     </row>
     <row r="701">
-      <c r="A701" s="90"/>
+      <c r="A701" s="89"/>
     </row>
     <row r="702">
-      <c r="A702" s="90"/>
+      <c r="A702" s="89"/>
     </row>
     <row r="703">
-      <c r="A703" s="90"/>
+      <c r="A703" s="89"/>
     </row>
     <row r="704">
-      <c r="A704" s="90"/>
+      <c r="A704" s="89"/>
     </row>
     <row r="705">
-      <c r="A705" s="90"/>
+      <c r="A705" s="89"/>
     </row>
     <row r="706">
-      <c r="A706" s="90"/>
+      <c r="A706" s="89"/>
     </row>
     <row r="707">
-      <c r="A707" s="90"/>
+      <c r="A707" s="89"/>
     </row>
     <row r="708">
-      <c r="A708" s="90"/>
+      <c r="A708" s="89"/>
     </row>
     <row r="709">
-      <c r="A709" s="90"/>
+      <c r="A709" s="89"/>
     </row>
     <row r="710">
-      <c r="A710" s="90"/>
+      <c r="A710" s="89"/>
     </row>
     <row r="711">
-      <c r="A711" s="90"/>
+      <c r="A711" s="89"/>
     </row>
     <row r="712">
-      <c r="A712" s="90"/>
+      <c r="A712" s="89"/>
     </row>
     <row r="713">
-      <c r="A713" s="90"/>
+      <c r="A713" s="89"/>
     </row>
     <row r="714">
-      <c r="A714" s="90"/>
+      <c r="A714" s="89"/>
     </row>
     <row r="715">
-      <c r="A715" s="90"/>
+      <c r="A715" s="89"/>
     </row>
     <row r="716">
-      <c r="A716" s="90"/>
+      <c r="A716" s="89"/>
     </row>
     <row r="717">
-      <c r="A717" s="90"/>
+      <c r="A717" s="89"/>
     </row>
     <row r="718">
-      <c r="A718" s="90"/>
+      <c r="A718" s="89"/>
     </row>
     <row r="719">
-      <c r="A719" s="90"/>
+      <c r="A719" s="89"/>
     </row>
     <row r="720">
-      <c r="A720" s="90"/>
+      <c r="A720" s="89"/>
     </row>
     <row r="721">
-      <c r="A721" s="90"/>
+      <c r="A721" s="89"/>
     </row>
     <row r="722">
-      <c r="A722" s="90"/>
+      <c r="A722" s="89"/>
     </row>
     <row r="723">
-      <c r="A723" s="90"/>
+      <c r="A723" s="89"/>
     </row>
     <row r="724">
-      <c r="A724" s="90"/>
+      <c r="A724" s="89"/>
     </row>
     <row r="725">
-      <c r="A725" s="90"/>
+      <c r="A725" s="89"/>
     </row>
     <row r="726">
-      <c r="A726" s="90"/>
+      <c r="A726" s="89"/>
     </row>
     <row r="727">
-      <c r="A727" s="90"/>
+      <c r="A727" s="89"/>
     </row>
     <row r="728">
-      <c r="A728" s="90"/>
+      <c r="A728" s="89"/>
     </row>
     <row r="729">
-      <c r="A729" s="90"/>
+      <c r="A729" s="89"/>
     </row>
     <row r="730">
-      <c r="A730" s="90"/>
+      <c r="A730" s="89"/>
     </row>
     <row r="731">
-      <c r="A731" s="90"/>
+      <c r="A731" s="89"/>
     </row>
     <row r="732">
-      <c r="A732" s="90"/>
+      <c r="A732" s="89"/>
     </row>
     <row r="733">
-      <c r="A733" s="90"/>
+      <c r="A733" s="89"/>
     </row>
     <row r="734">
-      <c r="A734" s="90"/>
+      <c r="A734" s="89"/>
     </row>
     <row r="735">
-      <c r="A735" s="90"/>
+      <c r="A735" s="89"/>
     </row>
     <row r="736">
-      <c r="A736" s="90"/>
+      <c r="A736" s="89"/>
     </row>
     <row r="737">
-      <c r="A737" s="90"/>
+      <c r="A737" s="89"/>
     </row>
     <row r="738">
-      <c r="A738" s="90"/>
+      <c r="A738" s="89"/>
     </row>
     <row r="739">
-      <c r="A739" s="90"/>
+      <c r="A739" s="89"/>
     </row>
     <row r="740">
-      <c r="A740" s="90"/>
+      <c r="A740" s="89"/>
     </row>
     <row r="741">
-      <c r="A741" s="90"/>
+      <c r="A741" s="89"/>
     </row>
     <row r="742">
-      <c r="A742" s="90"/>
+      <c r="A742" s="89"/>
     </row>
     <row r="743">
-      <c r="A743" s="90"/>
+      <c r="A743" s="89"/>
     </row>
     <row r="744">
-      <c r="A744" s="90"/>
+      <c r="A744" s="89"/>
     </row>
     <row r="745">
-      <c r="A745" s="90"/>
+      <c r="A745" s="89"/>
     </row>
     <row r="746">
-      <c r="A746" s="90"/>
+      <c r="A746" s="89"/>
     </row>
     <row r="747">
-      <c r="A747" s="90"/>
+      <c r="A747" s="89"/>
     </row>
     <row r="748">
-      <c r="A748" s="90"/>
+      <c r="A748" s="89"/>
     </row>
     <row r="749">
-      <c r="A749" s="90"/>
+      <c r="A749" s="89"/>
     </row>
     <row r="750">
-      <c r="A750" s="90"/>
+      <c r="A750" s="89"/>
     </row>
     <row r="751">
-      <c r="A751" s="90"/>
+      <c r="A751" s="89"/>
     </row>
     <row r="752">
-      <c r="A752" s="90"/>
+      <c r="A752" s="89"/>
     </row>
     <row r="753">
-      <c r="A753" s="90"/>
+      <c r="A753" s="89"/>
     </row>
     <row r="754">
-      <c r="A754" s="90"/>
+      <c r="A754" s="89"/>
     </row>
     <row r="755">
-      <c r="A755" s="90"/>
+      <c r="A755" s="89"/>
     </row>
     <row r="756">
-      <c r="A756" s="90"/>
+      <c r="A756" s="89"/>
     </row>
     <row r="757">
-      <c r="A757" s="90"/>
+      <c r="A757" s="89"/>
     </row>
     <row r="758">
-      <c r="A758" s="90"/>
+      <c r="A758" s="89"/>
     </row>
     <row r="759">
-      <c r="A759" s="90"/>
+      <c r="A759" s="89"/>
     </row>
     <row r="760">
-      <c r="A760" s="90"/>
+      <c r="A760" s="89"/>
     </row>
     <row r="761">
-      <c r="A761" s="90"/>
+      <c r="A761" s="89"/>
     </row>
     <row r="762">
-      <c r="A762" s="90"/>
+      <c r="A762" s="89"/>
     </row>
     <row r="763">
-      <c r="A763" s="90"/>
+      <c r="A763" s="89"/>
     </row>
     <row r="764">
-      <c r="A764" s="90"/>
+      <c r="A764" s="89"/>
     </row>
     <row r="765">
-      <c r="A765" s="90"/>
+      <c r="A765" s="89"/>
     </row>
     <row r="766">
-      <c r="A766" s="90"/>
+      <c r="A766" s="89"/>
     </row>
     <row r="767">
-      <c r="A767" s="90"/>
+      <c r="A767" s="89"/>
     </row>
     <row r="768">
-      <c r="A768" s="90"/>
+      <c r="A768" s="89"/>
     </row>
     <row r="769">
-      <c r="A769" s="90"/>
+      <c r="A769" s="89"/>
     </row>
     <row r="770">
-      <c r="A770" s="90"/>
+      <c r="A770" s="89"/>
     </row>
     <row r="771">
-      <c r="A771" s="90"/>
+      <c r="A771" s="89"/>
     </row>
     <row r="772">
-      <c r="A772" s="90"/>
+      <c r="A772" s="89"/>
     </row>
     <row r="773">
-      <c r="A773" s="90"/>
+      <c r="A773" s="89"/>
     </row>
     <row r="774">
-      <c r="A774" s="90"/>
+      <c r="A774" s="89"/>
     </row>
     <row r="775">
-      <c r="A775" s="90"/>
+      <c r="A775" s="89"/>
     </row>
     <row r="776">
-      <c r="A776" s="90"/>
+      <c r="A776" s="89"/>
     </row>
     <row r="777">
-      <c r="A777" s="90"/>
+      <c r="A777" s="89"/>
     </row>
     <row r="778">
-      <c r="A778" s="90"/>
+      <c r="A778" s="89"/>
     </row>
     <row r="779">
-      <c r="A779" s="90"/>
+      <c r="A779" s="89"/>
     </row>
     <row r="780">
-      <c r="A780" s="90"/>
+      <c r="A780" s="89"/>
     </row>
     <row r="781">
-      <c r="A781" s="90"/>
+      <c r="A781" s="89"/>
     </row>
     <row r="782">
-      <c r="A782" s="90"/>
+      <c r="A782" s="89"/>
     </row>
     <row r="783">
-      <c r="A783" s="90"/>
+      <c r="A783" s="89"/>
     </row>
     <row r="784">
-      <c r="A784" s="90"/>
+      <c r="A784" s="89"/>
     </row>
     <row r="785">
-      <c r="A785" s="90"/>
+      <c r="A785" s="89"/>
     </row>
     <row r="786">
-      <c r="A786" s="90"/>
+      <c r="A786" s="89"/>
     </row>
     <row r="787">
-      <c r="A787" s="90"/>
+      <c r="A787" s="89"/>
     </row>
     <row r="788">
-      <c r="A788" s="90"/>
+      <c r="A788" s="89"/>
     </row>
     <row r="789">
-      <c r="A789" s="90"/>
+      <c r="A789" s="89"/>
     </row>
     <row r="790">
-      <c r="A790" s="90"/>
+      <c r="A790" s="89"/>
     </row>
     <row r="791">
-      <c r="A791" s="90"/>
+      <c r="A791" s="89"/>
     </row>
     <row r="792">
-      <c r="A792" s="90"/>
+      <c r="A792" s="89"/>
     </row>
     <row r="793">
-      <c r="A793" s="90"/>
+      <c r="A793" s="89"/>
     </row>
     <row r="794">
-      <c r="A794" s="90"/>
+      <c r="A794" s="89"/>
     </row>
     <row r="795">
-      <c r="A795" s="90"/>
+      <c r="A795" s="89"/>
     </row>
     <row r="796">
-      <c r="A796" s="90"/>
+      <c r="A796" s="89"/>
     </row>
     <row r="797">
-      <c r="A797" s="90"/>
+      <c r="A797" s="89"/>
     </row>
     <row r="798">
-      <c r="A798" s="90"/>
+      <c r="A798" s="89"/>
     </row>
     <row r="799">
-      <c r="A799" s="90"/>
+      <c r="A799" s="89"/>
     </row>
     <row r="800">
-      <c r="A800" s="90"/>
+      <c r="A800" s="89"/>
     </row>
     <row r="801">
-      <c r="A801" s="90"/>
+      <c r="A801" s="89"/>
     </row>
     <row r="802">
-      <c r="A802" s="90"/>
+      <c r="A802" s="89"/>
     </row>
     <row r="803">
-      <c r="A803" s="90"/>
+      <c r="A803" s="89"/>
     </row>
     <row r="804">
-      <c r="A804" s="90"/>
+      <c r="A804" s="89"/>
     </row>
     <row r="805">
-      <c r="A805" s="90"/>
+      <c r="A805" s="89"/>
     </row>
     <row r="806">
-      <c r="A806" s="90"/>
+      <c r="A806" s="89"/>
     </row>
     <row r="807">
-      <c r="A807" s="90"/>
+      <c r="A807" s="89"/>
     </row>
     <row r="808">
-      <c r="A808" s="90"/>
+      <c r="A808" s="89"/>
     </row>
     <row r="809">
-      <c r="A809" s="90"/>
+      <c r="A809" s="89"/>
     </row>
     <row r="810">
-      <c r="A810" s="90"/>
+      <c r="A810" s="89"/>
     </row>
     <row r="811">
-      <c r="A811" s="90"/>
+      <c r="A811" s="89"/>
     </row>
     <row r="812">
-      <c r="A812" s="90"/>
+      <c r="A812" s="89"/>
     </row>
     <row r="813">
-      <c r="A813" s="90"/>
+      <c r="A813" s="89"/>
     </row>
     <row r="814">
-      <c r="A814" s="90"/>
+      <c r="A814" s="89"/>
     </row>
     <row r="815">
-      <c r="A815" s="90"/>
+      <c r="A815" s="89"/>
     </row>
     <row r="816">
-      <c r="A816" s="90"/>
+      <c r="A816" s="89"/>
     </row>
     <row r="817">
-      <c r="A817" s="90"/>
+      <c r="A817" s="89"/>
     </row>
     <row r="818">
-      <c r="A818" s="90"/>
+      <c r="A818" s="89"/>
     </row>
     <row r="819">
-      <c r="A819" s="90"/>
+      <c r="A819" s="89"/>
     </row>
     <row r="820">
-      <c r="A820" s="90"/>
+      <c r="A820" s="89"/>
     </row>
     <row r="821">
-      <c r="A821" s="90"/>
+      <c r="A821" s="89"/>
     </row>
     <row r="822">
-      <c r="A822" s="90"/>
+      <c r="A822" s="89"/>
     </row>
     <row r="823">
-      <c r="A823" s="90"/>
+      <c r="A823" s="89"/>
     </row>
     <row r="824">
-      <c r="A824" s="90"/>
+      <c r="A824" s="89"/>
     </row>
     <row r="825">
-      <c r="A825" s="90"/>
+      <c r="A825" s="89"/>
     </row>
     <row r="826">
-      <c r="A826" s="90"/>
+      <c r="A826" s="89"/>
     </row>
     <row r="827">
-      <c r="A827" s="90"/>
+      <c r="A827" s="89"/>
     </row>
     <row r="828">
-      <c r="A828" s="90"/>
+      <c r="A828" s="89"/>
     </row>
     <row r="829">
-      <c r="A829" s="90"/>
+      <c r="A829" s="89"/>
     </row>
     <row r="830">
-      <c r="A830" s="90"/>
+      <c r="A830" s="89"/>
     </row>
     <row r="831">
-      <c r="A831" s="90"/>
+      <c r="A831" s="89"/>
     </row>
     <row r="832">
-      <c r="A832" s="90"/>
+      <c r="A832" s="89"/>
     </row>
     <row r="833">
-      <c r="A833" s="90"/>
+      <c r="A833" s="89"/>
     </row>
     <row r="834">
-      <c r="A834" s="90"/>
+      <c r="A834" s="89"/>
     </row>
     <row r="835">
-      <c r="A835" s="90"/>
+      <c r="A835" s="89"/>
     </row>
     <row r="836">
-      <c r="A836" s="90"/>
+      <c r="A836" s="89"/>
     </row>
     <row r="837">
-      <c r="A837" s="90"/>
+      <c r="A837" s="89"/>
     </row>
     <row r="838">
-      <c r="A838" s="90"/>
+      <c r="A838" s="89"/>
     </row>
     <row r="839">
-      <c r="A839" s="90"/>
+      <c r="A839" s="89"/>
     </row>
     <row r="840">
-      <c r="A840" s="90"/>
+      <c r="A840" s="89"/>
     </row>
     <row r="841">
-      <c r="A841" s="90"/>
+      <c r="A841" s="89"/>
     </row>
     <row r="842">
-      <c r="A842" s="90"/>
+      <c r="A842" s="89"/>
     </row>
     <row r="843">
-      <c r="A843" s="90"/>
+      <c r="A843" s="89"/>
     </row>
     <row r="844">
-      <c r="A844" s="90"/>
+      <c r="A844" s="89"/>
     </row>
     <row r="845">
-      <c r="A845" s="90"/>
+      <c r="A845" s="89"/>
     </row>
     <row r="846">
-      <c r="A846" s="90"/>
+      <c r="A846" s="89"/>
     </row>
     <row r="847">
-      <c r="A847" s="90"/>
+      <c r="A847" s="89"/>
     </row>
     <row r="848">
-      <c r="A848" s="90"/>
+      <c r="A848" s="89"/>
     </row>
     <row r="849">
-      <c r="A849" s="90"/>
+      <c r="A849" s="89"/>
     </row>
     <row r="850">
-      <c r="A850" s="90"/>
+      <c r="A850" s="89"/>
     </row>
     <row r="851">
-      <c r="A851" s="90"/>
+      <c r="A851" s="89"/>
     </row>
     <row r="852">
-      <c r="A852" s="90"/>
+      <c r="A852" s="89"/>
     </row>
     <row r="853">
-      <c r="A853" s="90"/>
+      <c r="A853" s="89"/>
     </row>
     <row r="854">
-      <c r="A854" s="90"/>
+      <c r="A854" s="89"/>
     </row>
     <row r="855">
-      <c r="A855" s="90"/>
+      <c r="A855" s="89"/>
     </row>
     <row r="856">
-      <c r="A856" s="90"/>
+      <c r="A856" s="89"/>
     </row>
     <row r="857">
-      <c r="A857" s="90"/>
+      <c r="A857" s="89"/>
     </row>
     <row r="858">
-      <c r="A858" s="90"/>
+      <c r="A858" s="89"/>
     </row>
     <row r="859">
-      <c r="A859" s="90"/>
+      <c r="A859" s="89"/>
     </row>
     <row r="860">
-      <c r="A860" s="90"/>
+      <c r="A860" s="89"/>
     </row>
     <row r="861">
-      <c r="A861" s="90"/>
+      <c r="A861" s="89"/>
     </row>
     <row r="862">
-      <c r="A862" s="90"/>
+      <c r="A862" s="89"/>
     </row>
     <row r="863">
-      <c r="A863" s="90"/>
+      <c r="A863" s="89"/>
     </row>
     <row r="864">
-      <c r="A864" s="90"/>
+      <c r="A864" s="89"/>
     </row>
     <row r="865">
-      <c r="A865" s="90"/>
+      <c r="A865" s="89"/>
     </row>
     <row r="866">
-      <c r="A866" s="90"/>
+      <c r="A866" s="89"/>
     </row>
     <row r="867">
-      <c r="A867" s="90"/>
+      <c r="A867" s="89"/>
     </row>
     <row r="868">
-      <c r="A868" s="90"/>
+      <c r="A868" s="89"/>
     </row>
     <row r="869">
-      <c r="A869" s="90"/>
+      <c r="A869" s="89"/>
     </row>
     <row r="870">
-      <c r="A870" s="90"/>
+      <c r="A870" s="89"/>
     </row>
     <row r="871">
-      <c r="A871" s="90"/>
+      <c r="A871" s="89"/>
     </row>
     <row r="872">
-      <c r="A872" s="90"/>
+      <c r="A872" s="89"/>
     </row>
     <row r="873">
-      <c r="A873" s="90"/>
+      <c r="A873" s="89"/>
     </row>
     <row r="874">
-      <c r="A874" s="90"/>
+      <c r="A874" s="89"/>
     </row>
     <row r="875">
-      <c r="A875" s="90"/>
+      <c r="A875" s="89"/>
     </row>
     <row r="876">
-      <c r="A876" s="90"/>
+      <c r="A876" s="89"/>
     </row>
     <row r="877">
-      <c r="A877" s="90"/>
+      <c r="A877" s="89"/>
     </row>
     <row r="878">
-      <c r="A878" s="90"/>
+      <c r="A878" s="89"/>
     </row>
     <row r="879">
-      <c r="A879" s="90"/>
+      <c r="A879" s="89"/>
     </row>
     <row r="880">
-      <c r="A880" s="90"/>
+      <c r="A880" s="89"/>
     </row>
     <row r="881">
-      <c r="A881" s="90"/>
+      <c r="A881" s="89"/>
     </row>
     <row r="882">
-      <c r="A882" s="90"/>
+      <c r="A882" s="89"/>
     </row>
     <row r="883">
-      <c r="A883" s="90"/>
+      <c r="A883" s="89"/>
     </row>
     <row r="884">
-      <c r="A884" s="90"/>
+      <c r="A884" s="89"/>
     </row>
     <row r="885">
-      <c r="A885" s="90"/>
+      <c r="A885" s="89"/>
     </row>
     <row r="886">
-      <c r="A886" s="90"/>
+      <c r="A886" s="89"/>
     </row>
     <row r="887">
-      <c r="A887" s="90"/>
+      <c r="A887" s="89"/>
     </row>
     <row r="888">
-      <c r="A888" s="90"/>
+      <c r="A888" s="89"/>
     </row>
     <row r="889">
-      <c r="A889" s="90"/>
+      <c r="A889" s="89"/>
     </row>
     <row r="890">
-      <c r="A890" s="90"/>
+      <c r="A890" s="89"/>
     </row>
     <row r="891">
-      <c r="A891" s="90"/>
+      <c r="A891" s="89"/>
     </row>
     <row r="892">
-      <c r="A892" s="90"/>
+      <c r="A892" s="89"/>
     </row>
     <row r="893">
-      <c r="A893" s="90"/>
+      <c r="A893" s="89"/>
     </row>
     <row r="894">
-      <c r="A894" s="90"/>
+      <c r="A894" s="89"/>
     </row>
     <row r="895">
-      <c r="A895" s="90"/>
+      <c r="A895" s="89"/>
     </row>
     <row r="896">
-      <c r="A896" s="90"/>
+      <c r="A896" s="89"/>
     </row>
     <row r="897">
-      <c r="A897" s="90"/>
+      <c r="A897" s="89"/>
     </row>
     <row r="898">
-      <c r="A898" s="90"/>
+      <c r="A898" s="89"/>
     </row>
     <row r="899">
-      <c r="A899" s="90"/>
+      <c r="A899" s="89"/>
     </row>
     <row r="900">
-      <c r="A900" s="90"/>
+      <c r="A900" s="89"/>
     </row>
     <row r="901">
-      <c r="A901" s="90"/>
+      <c r="A901" s="89"/>
     </row>
     <row r="902">
-      <c r="A902" s="90"/>
+      <c r="A902" s="89"/>
     </row>
     <row r="903">
-      <c r="A903" s="90"/>
+      <c r="A903" s="89"/>
     </row>
     <row r="904">
-      <c r="A904" s="90"/>
+      <c r="A904" s="89"/>
     </row>
     <row r="905">
-      <c r="A905" s="90"/>
+      <c r="A905" s="89"/>
     </row>
     <row r="906">
-      <c r="A906" s="90"/>
+      <c r="A906" s="89"/>
     </row>
     <row r="907">
-      <c r="A907" s="90"/>
+      <c r="A907" s="89"/>
     </row>
     <row r="908">
-      <c r="A908" s="90"/>
+      <c r="A908" s="89"/>
     </row>
     <row r="909">
-      <c r="A909" s="90"/>
+      <c r="A909" s="89"/>
     </row>
     <row r="910">
-      <c r="A910" s="90"/>
+      <c r="A910" s="89"/>
     </row>
     <row r="911">
-      <c r="A911" s="90"/>
+      <c r="A911" s="89"/>
     </row>
     <row r="912">
-      <c r="A912" s="90"/>
+      <c r="A912" s="89"/>
     </row>
     <row r="913">
-      <c r="A913" s="90"/>
+      <c r="A913" s="89"/>
     </row>
     <row r="914">
-      <c r="A914" s="90"/>
+      <c r="A914" s="89"/>
     </row>
     <row r="915">
-      <c r="A915" s="90"/>
+      <c r="A915" s="89"/>
     </row>
     <row r="916">
-      <c r="A916" s="90"/>
+      <c r="A916" s="89"/>
     </row>
     <row r="917">
-      <c r="A917" s="90"/>
+      <c r="A917" s="89"/>
     </row>
     <row r="918">
-      <c r="A918" s="90"/>
+      <c r="A918" s="89"/>
     </row>
     <row r="919">
-      <c r="A919" s="90"/>
+      <c r="A919" s="89"/>
     </row>
     <row r="920">
-      <c r="A920" s="90"/>
+      <c r="A920" s="89"/>
     </row>
     <row r="921">
-      <c r="A921" s="90"/>
+      <c r="A921" s="89"/>
     </row>
     <row r="922">
-      <c r="A922" s="90"/>
+      <c r="A922" s="89"/>
     </row>
     <row r="923">
-      <c r="A923" s="90"/>
+      <c r="A923" s="89"/>
     </row>
     <row r="924">
-      <c r="A924" s="90"/>
+      <c r="A924" s="89"/>
     </row>
     <row r="925">
-      <c r="A925" s="90"/>
+      <c r="A925" s="89"/>
     </row>
     <row r="926">
-      <c r="A926" s="90"/>
+      <c r="A926" s="89"/>
     </row>
     <row r="927">
-      <c r="A927" s="90"/>
+      <c r="A927" s="89"/>
     </row>
     <row r="928">
-      <c r="A928" s="90"/>
+      <c r="A928" s="89"/>
     </row>
     <row r="929">
-      <c r="A929" s="90"/>
+      <c r="A929" s="89"/>
     </row>
     <row r="930">
-      <c r="A930" s="90"/>
+      <c r="A930" s="89"/>
     </row>
     <row r="931">
-      <c r="A931" s="90"/>
+      <c r="A931" s="89"/>
     </row>
     <row r="932">
-      <c r="A932" s="90"/>
+      <c r="A932" s="89"/>
     </row>
     <row r="933">
-      <c r="A933" s="90"/>
+      <c r="A933" s="89"/>
     </row>
     <row r="934">
-      <c r="A934" s="90"/>
+      <c r="A934" s="89"/>
     </row>
     <row r="935">
-      <c r="A935" s="90"/>
+      <c r="A935" s="89"/>
     </row>
     <row r="936">
-      <c r="A936" s="90"/>
+      <c r="A936" s="89"/>
     </row>
     <row r="937">
-      <c r="A937" s="90"/>
+      <c r="A937" s="89"/>
     </row>
     <row r="938">
-      <c r="A938" s="90"/>
+      <c r="A938" s="89"/>
     </row>
     <row r="939">
-      <c r="A939" s="90"/>
+      <c r="A939" s="89"/>
     </row>
     <row r="940">
-      <c r="A940" s="90"/>
+      <c r="A940" s="89"/>
     </row>
     <row r="941">
-      <c r="A941" s="90"/>
+      <c r="A941" s="89"/>
     </row>
     <row r="942">
-      <c r="A942" s="90"/>
+      <c r="A942" s="89"/>
     </row>
     <row r="943">
-      <c r="A943" s="90"/>
+      <c r="A943" s="89"/>
     </row>
     <row r="944">
-      <c r="A944" s="90"/>
+      <c r="A944" s="89"/>
     </row>
     <row r="945">
-      <c r="A945" s="90"/>
+      <c r="A945" s="89"/>
     </row>
     <row r="946">
-      <c r="A946" s="90"/>
+      <c r="A946" s="89"/>
     </row>
     <row r="947">
-      <c r="A947" s="90"/>
+      <c r="A947" s="89"/>
     </row>
     <row r="948">
-      <c r="A948" s="90"/>
+      <c r="A948" s="89"/>
     </row>
     <row r="949">
-      <c r="A949" s="90"/>
+      <c r="A949" s="89"/>
     </row>
     <row r="950">
-      <c r="A950" s="90"/>
+      <c r="A950" s="89"/>
     </row>
     <row r="951">
-      <c r="A951" s="90"/>
+      <c r="A951" s="89"/>
     </row>
     <row r="952">
-      <c r="A952" s="90"/>
+      <c r="A952" s="89"/>
     </row>
     <row r="953">
-      <c r="A953" s="90"/>
+      <c r="A953" s="89"/>
     </row>
     <row r="954">
-      <c r="A954" s="90"/>
+      <c r="A954" s="89"/>
     </row>
     <row r="955">
-      <c r="A955" s="90"/>
+      <c r="A955" s="89"/>
     </row>
     <row r="956">
-      <c r="A956" s="90"/>
+      <c r="A956" s="89"/>
     </row>
     <row r="957">
-      <c r="A957" s="90"/>
+      <c r="A957" s="89"/>
     </row>
     <row r="958">
-      <c r="A958" s="90"/>
+      <c r="A958" s="89"/>
     </row>
     <row r="959">
-      <c r="A959" s="90"/>
+      <c r="A959" s="89"/>
     </row>
     <row r="960">
-      <c r="A960" s="90"/>
+      <c r="A960" s="89"/>
     </row>
     <row r="961">
-      <c r="A961" s="90"/>
+      <c r="A961" s="89"/>
     </row>
     <row r="962">
-      <c r="A962" s="90"/>
+      <c r="A962" s="89"/>
     </row>
     <row r="963">
-      <c r="A963" s="90"/>
+      <c r="A963" s="89"/>
     </row>
     <row r="964">
-      <c r="A964" s="90"/>
+      <c r="A964" s="89"/>
     </row>
     <row r="965">
-      <c r="A965" s="90"/>
+      <c r="A965" s="89"/>
     </row>
     <row r="966">
-      <c r="A966" s="90"/>
+      <c r="A966" s="89"/>
     </row>
     <row r="967">
-      <c r="A967" s="90"/>
+      <c r="A967" s="89"/>
     </row>
     <row r="968">
-      <c r="A968" s="90"/>
+      <c r="A968" s="89"/>
     </row>
     <row r="969">
-      <c r="A969" s="90"/>
+      <c r="A969" s="89"/>
     </row>
     <row r="970">
-      <c r="A970" s="90"/>
+      <c r="A970" s="89"/>
     </row>
     <row r="971">
-      <c r="A971" s="90"/>
+      <c r="A971" s="89"/>
     </row>
     <row r="972">
-      <c r="A972" s="90"/>
+      <c r="A972" s="89"/>
     </row>
     <row r="973">
-      <c r="A973" s="90"/>
+      <c r="A973" s="89"/>
     </row>
     <row r="974">
-      <c r="A974" s="90"/>
+      <c r="A974" s="89"/>
     </row>
     <row r="975">
-      <c r="A975" s="90"/>
+      <c r="A975" s="89"/>
     </row>
     <row r="976">
-      <c r="A976" s="90"/>
+      <c r="A976" s="89"/>
     </row>
     <row r="977">
-      <c r="A977" s="90"/>
+      <c r="A977" s="89"/>
     </row>
     <row r="978">
-      <c r="A978" s="90"/>
+      <c r="A978" s="89"/>
     </row>
     <row r="979">
-      <c r="A979" s="90"/>
+      <c r="A979" s="89"/>
     </row>
     <row r="980">
-      <c r="A980" s="90"/>
+      <c r="A980" s="89"/>
     </row>
     <row r="981">
-      <c r="A981" s="90"/>
+      <c r="A981" s="89"/>
     </row>
     <row r="982">
-      <c r="A982" s="90"/>
+      <c r="A982" s="89"/>
     </row>
     <row r="983">
-      <c r="A983" s="90"/>
+      <c r="A983" s="89"/>
     </row>
     <row r="984">
-      <c r="A984" s="90"/>
+      <c r="A984" s="89"/>
     </row>
     <row r="985">
-      <c r="A985" s="90"/>
+      <c r="A985" s="89"/>
     </row>
     <row r="986">
-      <c r="A986" s="90"/>
+      <c r="A986" s="89"/>
     </row>
     <row r="987">
-      <c r="A987" s="90"/>
+      <c r="A987" s="89"/>
     </row>
     <row r="988">
-      <c r="A988" s="90"/>
+      <c r="A988" s="89"/>
     </row>
     <row r="989">
-      <c r="A989" s="90"/>
+      <c r="A989" s="89"/>
     </row>
     <row r="990">
-      <c r="A990" s="90"/>
+      <c r="A990" s="89"/>
     </row>
     <row r="991">
-      <c r="A991" s="90"/>
+      <c r="A991" s="89"/>
     </row>
     <row r="992">
-      <c r="A992" s="90"/>
+      <c r="A992" s="89"/>
     </row>
     <row r="993">
-      <c r="A993" s="90"/>
+      <c r="A993" s="89"/>
     </row>
     <row r="994">
-      <c r="A994" s="90"/>
+      <c r="A994" s="89"/>
     </row>
     <row r="995">
-      <c r="A995" s="90"/>
+      <c r="A995" s="89"/>
     </row>
     <row r="996">
-      <c r="A996" s="90"/>
+      <c r="A996" s="89"/>
     </row>
     <row r="997">
-      <c r="A997" s="90"/>
+      <c r="A997" s="89"/>
     </row>
     <row r="998">
-      <c r="A998" s="90"/>
+      <c r="A998" s="89"/>
     </row>
     <row r="999">
-      <c r="A999" s="90"/>
+      <c r="A999" s="89"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="90"/>
+      <c r="A1000" s="89"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="45" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="45" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="45" t="s">
-        <v>176</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -41974,7 +41910,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -42013,10 +41949,10 @@
         <v>87</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5">
@@ -42033,7 +41969,7 @@
         <v>15</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6">
@@ -42048,7 +41984,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="2"/>
@@ -42060,7 +41996,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -42089,7 +42025,7 @@
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -42100,7 +42036,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -42118,7 +42054,7 @@
         <v>232</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -42132,10 +42068,10 @@
         <v>26</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -42149,7 +42085,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12">
@@ -42163,25 +42099,25 @@
         <v>108</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O12" s="44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="75">
         <v>44470.0</v>
       </c>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="91" t="s">
         <v>281</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="44" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -42198,15 +42134,15 @@
       <c r="A14" s="75">
         <v>45597.0</v>
       </c>
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="91" t="s">
         <v>281</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -42224,7 +42160,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="45" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="45" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -42336,7 +42304,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -42375,10 +42343,10 @@
         <v>154</v>
       </c>
       <c r="E4" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="O4" s="46" t="s">
         <v>362</v>
-      </c>
-      <c r="O4" s="46" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -42393,7 +42361,7 @@
       </c>
       <c r="D5" s="50"/>
       <c r="E5" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="2"/>
@@ -42405,7 +42373,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -42420,7 +42388,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -42457,7 +42425,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8">
@@ -42474,7 +42442,7 @@
         <v>232</v>
       </c>
       <c r="N8" s="54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -42491,7 +42459,7 @@
         <v>187</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -42502,11 +42470,11 @@
         <v>198</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -42517,10 +42485,10 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="44" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -42542,16 +42510,16 @@
         <v>198</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E11" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="N11" s="45" t="s">
         <v>366</v>
       </c>
-      <c r="N11" s="45" t="s">
+      <c r="O11" s="45" t="s">
         <v>367</v>
-      </c>
-      <c r="O11" s="45" t="s">
-        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -42559,7 +42527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -42671,7 +42639,7 @@
         <v>42100.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="5" t="s">
@@ -42710,10 +42678,10 @@
         <v>87</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
@@ -42740,7 +42708,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6">
@@ -42755,7 +42723,7 @@
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="2"/>
@@ -42767,7 +42735,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -42834,7 +42802,7 @@
         <v>15</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -42849,7 +42817,7 @@
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -42860,7 +42828,7 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O10" s="5"/>
     </row>
@@ -42878,7 +42846,7 @@
         <v>232</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
@@ -42892,13 +42860,13 @@
         <v>26</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O12" s="45" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13">
@@ -42912,7 +42880,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14">
@@ -42926,7 +42894,7 @@
         <v>108</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
@@ -42934,19 +42902,19 @@
         <v>43748.0</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N15" s="45" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O15" s="45" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16">
@@ -42957,10 +42925,10 @@
         <v>198</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O16" s="45" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -42969,7 +42937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -43105,7 +43073,7 @@
         <v>15</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5">
@@ -43123,7 +43091,7 @@
         <v>232</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6">
@@ -43137,13 +43105,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -43161,7 +43129,7 @@
         <v>17</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8">
@@ -46148,7 +46116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -46287,7 +46255,7 @@
         <v>41</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>15</v>
@@ -46308,7 +46276,7 @@
         <v>232</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -46322,13 +46290,13 @@
         <v>41</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -46346,7 +46314,7 @@
         <v>17</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -50323,7 +50291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -50453,7 +50421,7 @@
       <c r="B4" s="51">
         <v>42251.0</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="92" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="46" t="s">
@@ -50461,7 +50429,7 @@
       </c>
       <c r="N4" s="46"/>
       <c r="O4" s="46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5">
@@ -50471,7 +50439,7 @@
       <c r="B5" s="51">
         <v>42255.0</v>
       </c>
-      <c r="C5" s="93" t="s">
+      <c r="C5" s="92" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="46" t="s">
@@ -50490,7 +50458,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>232</v>
@@ -50511,7 +50479,7 @@
         <v>187</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -50523,7 +50491,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -50533,7 +50501,7 @@
       <c r="B8" s="51">
         <v>42527.0</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="83" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="5"/>
@@ -50562,11 +50530,11 @@
         <v>41</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N9" s="46"/>
       <c r="O9" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -50584,7 +50552,7 @@
       </c>
       <c r="N10" s="46"/>
       <c r="O10" s="46" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11">
@@ -54574,7 +54542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -54699,7 +54667,7 @@
       <c r="B4" s="51">
         <v>42255.0</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="92" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="5"/>
@@ -54724,17 +54692,17 @@
       <c r="B5" s="51">
         <v>42321.0</v>
       </c>
-      <c r="C5" s="93" t="s">
+      <c r="C5" s="92" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
@@ -54751,10 +54719,10 @@
         <v>187</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
@@ -54768,16 +54736,16 @@
         <v>41</v>
       </c>
       <c r="D7" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="N7" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="O7" s="46" t="s">
         <v>386</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="N7" s="46" t="s">
-        <v>385</v>
-      </c>
-      <c r="O7" s="46" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="8">
@@ -54797,7 +54765,7 @@
         <v>15</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -54828,13 +54796,13 @@
         <v>162</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E10" s="46" t="s">
         <v>232</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
@@ -54857,16 +54825,16 @@
         <v>260</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O12" s="45" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -54874,7 +54842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -54997,7 +54965,7 @@
         <v>2</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
@@ -55007,17 +54975,17 @@
       <c r="B4" s="51">
         <v>42321.0</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="92" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>15</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
@@ -55034,10 +55002,10 @@
         <v>187</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
@@ -55051,13 +55019,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
@@ -55085,10 +55053,10 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
@@ -55108,7 +55076,7 @@
         <v>15</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -55122,7 +55090,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>232</v>
@@ -55136,7 +55104,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -55168,7 +55136,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12">
@@ -60118,6 +60086,146 @@
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" s="2">
+        <v>415.0</v>
+      </c>
+      <c r="I1" s="2">
+        <v>500.0</v>
+      </c>
+      <c r="J1" s="2">
+        <v>1625.0</v>
+      </c>
+      <c r="K1" s="2">
+        <v>675.0</v>
+      </c>
+      <c r="L1" s="2">
+        <v>860.0</v>
+      </c>
+      <c r="M1" s="2">
+        <v>940.0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="64">
+        <v>44545.0</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="O2" s="45" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="56">
+        <v>44256.0</v>
+      </c>
+      <c r="B3" s="56">
+        <v>44270.0</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="O3" s="93" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="E4" s="45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="68"/>
+      <c r="B5" s="71" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>399</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="44" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56">
+        <v>44409.0</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>402</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -60187,14 +60295,14 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="64">
-        <v>44545.0</v>
+      <c r="A2" s="55">
+        <v>44180.0</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="O2" s="45" t="s">
-        <v>396</v>
+        <v>394</v>
+      </c>
+      <c r="O2" s="94" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="3">
@@ -60208,28 +60316,33 @@
         <v>108</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>397</v>
-      </c>
-      <c r="O3" s="94" t="s">
-        <v>398</v>
+        <v>396</v>
+      </c>
+      <c r="O3" s="95" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="4">
       <c r="E4" s="45" t="s">
         <v>15</v>
       </c>
+      <c r="O4" s="45" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="68"/>
+      <c r="A5" s="68">
+        <v>44470.0</v>
+      </c>
       <c r="B5" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>399</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>400</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="44" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -60240,9 +60353,7 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
-      <c r="O5" s="44" t="s">
-        <v>402</v>
-      </c>
+      <c r="O5" s="5"/>
     </row>
     <row r="6">
       <c r="A6" s="56">
@@ -60252,7 +60363,7 @@
         <v>154</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -60269,138 +60380,161 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" s="2">
-        <v>415.0</v>
-      </c>
-      <c r="I1" s="2">
-        <v>500.0</v>
-      </c>
-      <c r="J1" s="2">
-        <v>1625.0</v>
-      </c>
-      <c r="K1" s="2">
-        <v>675.0</v>
-      </c>
-      <c r="L1" s="2">
-        <v>860.0</v>
-      </c>
-      <c r="M1" s="2">
-        <v>940.0</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
+      <c r="A1" s="58" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="55">
-        <v>44180.0</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="O2" s="95" t="s">
-        <v>404</v>
+      <c r="A2" s="58" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="56">
-        <v>44256.0</v>
-      </c>
-      <c r="B3" s="56">
-        <v>44270.0</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>397</v>
-      </c>
-      <c r="O3" s="96" t="s">
-        <v>405</v>
-      </c>
+      <c r="A3" s="96"/>
     </row>
     <row r="4">
-      <c r="E4" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="45" t="s">
-        <v>406</v>
+      <c r="A4" s="58" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68">
-        <v>44470.0</v>
-      </c>
-      <c r="B5" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>400</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="44" t="s">
-        <v>401</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="A5" s="96"/>
     </row>
     <row r="6">
-      <c r="A6" s="56">
-        <v>44409.0</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>403</v>
+      <c r="A6" s="58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="58" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="58" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="58" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="58" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="58" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="58" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="58" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="58" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="58" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="96"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="58" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="58" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="58" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="58" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="58" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="58" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="58" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="58" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -63560,172 +63694,6 @@
     </row>
     <row r="1000">
       <c r="D1000" s="46"/>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="58" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="58" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="97"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="58" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="97"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="58" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="58" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="58" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="58" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="58" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="58" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="58" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="58" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="58" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="58" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="58" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="58" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="58" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="58" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="58" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="58" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="58" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="97"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="58" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="58" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="58" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="58" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="58" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="58" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="58" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="58" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="58" t="s">
-        <v>434</v>
-      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
